--- a/TestData/Processing/DataProcess/Three solutions 2/Ref/Ethanol.xlsx
+++ b/TestData/Processing/DataProcess/Three solutions 2/Ref/Ethanol.xlsx
@@ -1,21 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24701"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhang an\Desktop\Research\paper\6.AnyEIS Software\AnyEIS\TestData\Processing\DataProcess\Three solutions 2\Ref\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhang an\Desktop\Research\AnyEIS\AnysEIS\testdata\process\Three solution\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{429DA883-29CC-47CB-9545-94D4D3EB4F2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A99095CE-EA21-4CD7-87A1-8B225BF4E715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Experiment" sheetId="4" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -109,9 +118,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -149,9 +158,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -184,9 +193,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -219,9 +245,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -395,10 +438,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E202"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:S202"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -406,7 +449,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -423,3405 +466,5405 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A3" s="1">
         <v>1000000</v>
       </c>
       <c r="B3" s="2">
-        <v>50621</v>
+        <v>37865.800000000003</v>
       </c>
       <c r="C3" s="2">
-        <v>-87.063000000000002</v>
+        <v>-22.501000000000001</v>
       </c>
       <c r="D3" s="2">
-        <v>2593.39</v>
+        <v>34983.199999999997</v>
       </c>
       <c r="E3" s="2">
-        <v>-50554.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-14491.2</v>
+      </c>
+      <c r="H3" s="1"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A4" s="1">
         <v>1000000</v>
       </c>
       <c r="B4" s="2">
-        <v>49906.6</v>
+        <v>38400.9</v>
       </c>
       <c r="C4" s="2">
-        <v>-87.46</v>
+        <v>-21.905000000000001</v>
       </c>
       <c r="D4" s="2">
-        <v>2211.29</v>
+        <v>35628.5</v>
       </c>
       <c r="E4" s="2">
-        <v>-49857.599999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-14326.2</v>
+      </c>
+      <c r="H4" s="1"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>1100000</v>
       </c>
       <c r="B5" s="2">
-        <v>45935.9</v>
+        <v>33650.6</v>
       </c>
       <c r="C5" s="2">
-        <v>-77.834999999999994</v>
+        <v>-24.481000000000002</v>
       </c>
       <c r="D5" s="2">
-        <v>9679.67</v>
+        <v>30625.4</v>
       </c>
       <c r="E5" s="2">
-        <v>-44904.4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-13944.4</v>
+      </c>
+      <c r="H5" s="1"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>1100000</v>
       </c>
       <c r="B6" s="2">
-        <v>45997</v>
+        <v>31955</v>
       </c>
       <c r="C6" s="2">
-        <v>-76.911000000000001</v>
+        <v>-24.016999999999999</v>
       </c>
       <c r="D6" s="2">
-        <v>10416.4</v>
+        <v>29188.5</v>
       </c>
       <c r="E6" s="2">
-        <v>-44802</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-13005.9</v>
+      </c>
+      <c r="H6" s="1"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
+      <c r="S6" s="2"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>1200000</v>
       </c>
       <c r="B7" s="2">
-        <v>42865.4</v>
+        <v>30876</v>
       </c>
       <c r="C7" s="2">
-        <v>-73.912999999999997</v>
+        <v>-22.094999999999999</v>
       </c>
       <c r="D7" s="2">
-        <v>11877.7</v>
+        <v>28608.400000000001</v>
       </c>
       <c r="E7" s="2">
-        <v>-41186.9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-11614</v>
+      </c>
+      <c r="H7" s="1"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>1200000</v>
       </c>
       <c r="B8" s="2">
-        <v>43040.4</v>
+        <v>31231.5</v>
       </c>
       <c r="C8" s="2">
-        <v>-72.72</v>
+        <v>-22.577999999999999</v>
       </c>
       <c r="D8" s="2">
-        <v>12784.7</v>
+        <v>28837.9</v>
       </c>
       <c r="E8" s="2">
-        <v>-41097.800000000003</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-11990.9</v>
+      </c>
+      <c r="H8" s="1"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
         <v>1300000</v>
       </c>
       <c r="B9" s="2">
-        <v>41405.800000000003</v>
+        <v>30522.2</v>
       </c>
       <c r="C9" s="2">
-        <v>-72.850999999999999</v>
+        <v>-23.92</v>
       </c>
       <c r="D9" s="2">
-        <v>12208.5</v>
+        <v>27900.799999999999</v>
       </c>
       <c r="E9" s="2">
-        <v>-39565</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-12375.4</v>
+      </c>
+      <c r="H9" s="1"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
         <v>1300000</v>
       </c>
       <c r="B10" s="2">
-        <v>41419.800000000003</v>
+        <v>30439.200000000001</v>
       </c>
       <c r="C10" s="2">
-        <v>-71.805000000000007</v>
+        <v>-23.704999999999998</v>
       </c>
       <c r="D10" s="2">
-        <v>12933.2</v>
+        <v>27870.9</v>
       </c>
       <c r="E10" s="2">
-        <v>-39348.9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-12237.5</v>
+      </c>
+      <c r="H10" s="1"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>1400000</v>
       </c>
       <c r="B11" s="2">
-        <v>39836.9</v>
+        <v>29664.2</v>
       </c>
       <c r="C11" s="2">
-        <v>-71.902000000000001</v>
+        <v>-24.013999999999999</v>
       </c>
       <c r="D11" s="2">
-        <v>12374.8</v>
+        <v>27096.7</v>
       </c>
       <c r="E11" s="2">
-        <v>-37866.199999999997</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-12072</v>
+      </c>
+      <c r="H11" s="1"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
+      <c r="S11" s="2"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>1400000</v>
       </c>
       <c r="B12" s="2">
-        <v>39528.400000000001</v>
+        <v>29476.2</v>
       </c>
       <c r="C12" s="2">
-        <v>-72.317999999999998</v>
+        <v>-24.879000000000001</v>
       </c>
       <c r="D12" s="2">
-        <v>12006.1</v>
+        <v>26740.7</v>
       </c>
       <c r="E12" s="2">
-        <v>-37661</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-12400.9</v>
+      </c>
+      <c r="H12" s="1"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+      <c r="S12" s="2"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
         <v>1500000</v>
       </c>
       <c r="B13" s="2">
-        <v>38510.800000000003</v>
+        <v>29484.3</v>
       </c>
       <c r="C13" s="2">
-        <v>-74.045000000000002</v>
+        <v>-26.858000000000001</v>
       </c>
       <c r="D13" s="2">
-        <v>10586</v>
+        <v>26303.9</v>
       </c>
       <c r="E13" s="2">
-        <v>-37027.300000000003</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-13320.4</v>
+      </c>
+      <c r="H13" s="1"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
+      <c r="S13" s="2"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
         <v>1600000</v>
       </c>
       <c r="B14" s="2">
-        <v>37012.800000000003</v>
+        <v>29425.8</v>
       </c>
       <c r="C14" s="2">
-        <v>-76.759</v>
+        <v>-28.193000000000001</v>
       </c>
       <c r="D14" s="2">
-        <v>8477.6299999999992</v>
+        <v>25934.9</v>
       </c>
       <c r="E14" s="2">
-        <v>-36028.800000000003</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-13901.9</v>
+      </c>
+      <c r="H14" s="1"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="2"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
         <v>1600000</v>
       </c>
       <c r="B15" s="2">
-        <v>36959.599999999999</v>
+        <v>30002.1</v>
       </c>
       <c r="C15" s="2">
-        <v>-77.757000000000005</v>
+        <v>-27.655999999999999</v>
       </c>
       <c r="D15" s="2">
-        <v>7837.48</v>
+        <v>26574.400000000001</v>
       </c>
       <c r="E15" s="2">
-        <v>-36119.1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-13925.8</v>
+      </c>
+      <c r="H15" s="1"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
         <v>1700000</v>
       </c>
       <c r="B16" s="2">
-        <v>35221.9</v>
+        <v>30609.8</v>
       </c>
       <c r="C16" s="2">
-        <v>-81.007000000000005</v>
+        <v>-30.736999999999998</v>
       </c>
       <c r="D16" s="2">
-        <v>5505.52</v>
+        <v>26309.9</v>
       </c>
       <c r="E16" s="2">
-        <v>-34788.9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-15644.4</v>
+      </c>
+      <c r="H16" s="1"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
         <v>1800000</v>
       </c>
       <c r="B17" s="2">
-        <v>33239.699999999997</v>
+        <v>31622.6</v>
       </c>
       <c r="C17" s="2">
-        <v>-85.241</v>
+        <v>-35.503999999999998</v>
       </c>
       <c r="D17" s="2">
-        <v>2757.77</v>
+        <v>25743.1</v>
       </c>
       <c r="E17" s="2">
-        <v>-33125.1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-18365.2</v>
+      </c>
+      <c r="H17" s="1"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
         <v>1800000</v>
       </c>
       <c r="B18" s="2">
-        <v>33093.9</v>
+        <v>30463.3</v>
       </c>
       <c r="C18" s="2">
-        <v>-85.457999999999998</v>
+        <v>-34.618000000000002</v>
       </c>
       <c r="D18" s="2">
-        <v>2620.85</v>
+        <v>25070.1</v>
       </c>
       <c r="E18" s="2">
-        <v>-32990</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-17306.099999999999</v>
+      </c>
+      <c r="H18" s="1"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="O18" s="1"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
         <v>1900000</v>
       </c>
       <c r="B19" s="2">
-        <v>34503</v>
+        <v>32017.1</v>
       </c>
       <c r="C19" s="2">
-        <v>-85.822999999999993</v>
+        <v>-34.700000000000003</v>
       </c>
       <c r="D19" s="2">
-        <v>2513.35</v>
+        <v>26322.5</v>
       </c>
       <c r="E19" s="2">
-        <v>-34411.4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-18226.900000000001</v>
+      </c>
+      <c r="H19" s="1"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2"/>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
         <v>2000000</v>
       </c>
       <c r="B20" s="2">
-        <v>39197.5</v>
+        <v>33073.699999999997</v>
       </c>
       <c r="C20" s="2">
-        <v>-84.578999999999994</v>
+        <v>-28.696999999999999</v>
       </c>
       <c r="D20" s="2">
-        <v>3703.04</v>
+        <v>29011.4</v>
       </c>
       <c r="E20" s="2">
-        <v>-39022.1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-15881.1</v>
+      </c>
+      <c r="H20" s="1"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
+      <c r="S20" s="2"/>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
         <v>2100000</v>
       </c>
       <c r="B21" s="2">
-        <v>42836.4</v>
+        <v>35057.199999999997</v>
       </c>
       <c r="C21" s="2">
-        <v>-82.963999999999999</v>
+        <v>-21.593</v>
       </c>
       <c r="D21" s="2">
-        <v>5247.25</v>
+        <v>32597</v>
       </c>
       <c r="E21" s="2">
-        <v>-42513.8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-12901.3</v>
+      </c>
+      <c r="H21" s="1"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2"/>
+      <c r="S21" s="2"/>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
         <v>2100000</v>
       </c>
       <c r="B22" s="2">
-        <v>42667.1</v>
+        <v>34450.5</v>
       </c>
       <c r="C22" s="2">
-        <v>-81.570999999999998</v>
+        <v>-20.84</v>
       </c>
       <c r="D22" s="2">
-        <v>6254.55</v>
+        <v>32196.6</v>
       </c>
       <c r="E22" s="2">
-        <v>-42206.2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-12256.3</v>
+      </c>
+      <c r="H22" s="1"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="O22" s="1"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="2"/>
+      <c r="S22" s="2"/>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A23" s="1">
         <v>2200000</v>
       </c>
       <c r="B23" s="2">
-        <v>42621.5</v>
+        <v>33911.800000000003</v>
       </c>
       <c r="C23" s="2">
-        <v>-82.103999999999999</v>
+        <v>-18.713999999999999</v>
       </c>
       <c r="D23" s="2">
-        <v>5855.25</v>
+        <v>32119</v>
       </c>
       <c r="E23" s="2">
-        <v>-42217.4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-10880.1</v>
+      </c>
+      <c r="H23" s="1"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="2"/>
+      <c r="S23" s="2"/>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
         <v>2300000</v>
       </c>
       <c r="B24" s="2">
-        <v>40784.300000000003</v>
+        <v>33878.300000000003</v>
       </c>
       <c r="C24" s="2">
-        <v>-82.745999999999995</v>
+        <v>-19.007999999999999</v>
       </c>
       <c r="D24" s="2">
-        <v>5149.75</v>
+        <v>32031</v>
       </c>
       <c r="E24" s="2">
-        <v>-40457.9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-11034.2</v>
+      </c>
+      <c r="H24" s="1"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2"/>
+      <c r="S24" s="2"/>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A25" s="1">
         <v>2400000</v>
       </c>
       <c r="B25" s="2">
-        <v>38760.6</v>
+        <v>33725.9</v>
       </c>
       <c r="C25" s="2">
-        <v>-83.073999999999998</v>
+        <v>-21.515999999999998</v>
       </c>
       <c r="D25" s="2">
-        <v>4674.05</v>
+        <v>31375.7</v>
       </c>
       <c r="E25" s="2">
-        <v>-38477.800000000003</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-12369.5</v>
+      </c>
+      <c r="H25" s="1"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="2"/>
+      <c r="S25" s="2"/>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A26" s="1">
         <v>2500000</v>
       </c>
       <c r="B26" s="2">
-        <v>36337.4</v>
+        <v>33484.800000000003</v>
       </c>
       <c r="C26" s="2">
-        <v>-83.71</v>
+        <v>-23.193000000000001</v>
       </c>
       <c r="D26" s="2">
-        <v>3981.43</v>
+        <v>30778.6</v>
       </c>
       <c r="E26" s="2">
-        <v>-36118.6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-13187.5</v>
+      </c>
+      <c r="H26" s="1"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="2"/>
+      <c r="S26" s="2"/>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
         <v>2600000</v>
       </c>
       <c r="B27" s="2">
-        <v>33715.9</v>
+        <v>33237</v>
       </c>
       <c r="C27" s="2">
-        <v>-84.775999999999996</v>
+        <v>-25.234999999999999</v>
       </c>
       <c r="D27" s="2">
-        <v>3069.7</v>
+        <v>30065</v>
       </c>
       <c r="E27" s="2">
-        <v>-33575.9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-14170.1</v>
+      </c>
+      <c r="H27" s="1"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="2"/>
+      <c r="Q27" s="2"/>
+      <c r="R27" s="2"/>
+      <c r="S27" s="2"/>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A28" s="1">
         <v>2700000</v>
       </c>
       <c r="B28" s="2">
-        <v>31342.7</v>
+        <v>32653.9</v>
       </c>
       <c r="C28" s="2">
-        <v>-85.41</v>
+        <v>-27.425000000000001</v>
       </c>
       <c r="D28" s="2">
-        <v>2508.4</v>
+        <v>28984.2</v>
       </c>
       <c r="E28" s="2">
-        <v>-31242.2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-15039.9</v>
+      </c>
+      <c r="H28" s="1"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2"/>
+      <c r="S28" s="2"/>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A29" s="1">
         <v>2800000</v>
       </c>
       <c r="B29" s="2">
-        <v>28958.5</v>
+        <v>31703.4</v>
       </c>
       <c r="C29" s="2">
-        <v>-86.814999999999998</v>
+        <v>-31.469000000000001</v>
       </c>
       <c r="D29" s="2">
-        <v>1608.9</v>
+        <v>27040.6</v>
       </c>
       <c r="E29" s="2">
-        <v>-28913.8</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-16550.3</v>
+      </c>
+      <c r="H29" s="1"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="2"/>
+      <c r="R29" s="2"/>
+      <c r="S29" s="2"/>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A30" s="1">
         <v>3000000</v>
       </c>
       <c r="B30" s="2">
-        <v>24677.9</v>
+        <v>29829.5</v>
       </c>
       <c r="C30" s="2">
-        <v>-89.022000000000006</v>
+        <v>-38.805</v>
       </c>
       <c r="D30" s="2">
-        <v>421.08499999999998</v>
+        <v>23245.5</v>
       </c>
       <c r="E30" s="2">
-        <v>-24674.3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-18693.5</v>
+      </c>
+      <c r="H30" s="1"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="O30" s="1"/>
+      <c r="P30" s="2"/>
+      <c r="Q30" s="2"/>
+      <c r="R30" s="2"/>
+      <c r="S30" s="2"/>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A31" s="1">
         <v>3100000</v>
       </c>
       <c r="B31" s="2">
-        <v>23718.799999999999</v>
+        <v>29767.7</v>
       </c>
       <c r="C31" s="2">
-        <v>-89.486000000000004</v>
+        <v>-39.975999999999999</v>
       </c>
       <c r="D31" s="2">
-        <v>212.74600000000001</v>
+        <v>22811.3</v>
       </c>
       <c r="E31" s="2">
-        <v>-23717.9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-19124.8</v>
+      </c>
+      <c r="H31" s="1"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="2"/>
+      <c r="R31" s="2"/>
+      <c r="S31" s="2"/>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A32" s="1">
         <v>3200000</v>
       </c>
       <c r="B32" s="2">
-        <v>23078</v>
+        <v>29389.3</v>
       </c>
       <c r="C32" s="2">
-        <v>-89.153999999999996</v>
+        <v>-41.527999999999999</v>
       </c>
       <c r="D32" s="2">
-        <v>340.67099999999999</v>
+        <v>22001.599999999999</v>
       </c>
       <c r="E32" s="2">
-        <v>-23075.4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-19484.900000000001</v>
+      </c>
+      <c r="H32" s="1"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="2"/>
+      <c r="Q32" s="2"/>
+      <c r="R32" s="2"/>
+      <c r="S32" s="2"/>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A33" s="1">
         <v>3300000</v>
       </c>
       <c r="B33" s="2">
-        <v>22571.3</v>
+        <v>29344.7</v>
       </c>
       <c r="C33" s="2">
-        <v>-89.391999999999996</v>
+        <v>-42.55</v>
       </c>
       <c r="D33" s="2">
-        <v>239.68199999999999</v>
+        <v>21618</v>
       </c>
       <c r="E33" s="2">
-        <v>-22570.1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-19843.8</v>
+      </c>
+      <c r="H33" s="1"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="2"/>
+      <c r="Q33" s="2"/>
+      <c r="R33" s="2"/>
+      <c r="S33" s="2"/>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A34" s="1">
         <v>3500000</v>
       </c>
       <c r="B34" s="2">
-        <v>21553.599999999999</v>
+        <v>28657.1</v>
       </c>
       <c r="C34" s="2">
-        <v>-89.259</v>
+        <v>-43.262999999999998</v>
       </c>
       <c r="D34" s="2">
-        <v>278.77600000000001</v>
+        <v>20868.7</v>
       </c>
       <c r="E34" s="2">
-        <v>-21551.8</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-19640</v>
+      </c>
+      <c r="H34" s="1"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="O34" s="1"/>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="2"/>
+      <c r="R34" s="2"/>
+      <c r="S34" s="2"/>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A35" s="1">
         <v>3600000</v>
       </c>
       <c r="B35" s="2">
-        <v>20884.7</v>
+        <v>28474</v>
       </c>
       <c r="C35" s="2">
-        <v>-89.366</v>
+        <v>-44.703000000000003</v>
       </c>
       <c r="D35" s="2">
-        <v>230.96199999999999</v>
+        <v>20238.2</v>
       </c>
       <c r="E35" s="2">
-        <v>-20883.400000000001</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-20029.599999999999</v>
+      </c>
+      <c r="H35" s="1"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+      <c r="O35" s="1"/>
+      <c r="P35" s="2"/>
+      <c r="Q35" s="2"/>
+      <c r="R35" s="2"/>
+      <c r="S35" s="2"/>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A36" s="1">
         <v>3800000</v>
       </c>
       <c r="B36" s="2">
-        <v>20042.7</v>
+        <v>27514.6</v>
       </c>
       <c r="C36" s="2">
-        <v>-89.637</v>
+        <v>-44.658999999999999</v>
       </c>
       <c r="D36" s="2">
-        <v>126.944</v>
+        <v>19571.3</v>
       </c>
       <c r="E36" s="2">
-        <v>-20042.3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-19339.5</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="O36" s="1"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2"/>
+      <c r="R36" s="2"/>
+      <c r="S36" s="2"/>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A37" s="1">
         <v>3900000</v>
       </c>
       <c r="B37" s="2">
-        <v>19367.3</v>
+        <v>27171.4</v>
       </c>
       <c r="C37" s="2">
-        <v>-89.311999999999998</v>
+        <v>-44.701000000000001</v>
       </c>
       <c r="D37" s="2">
-        <v>232.435</v>
+        <v>19313</v>
       </c>
       <c r="E37" s="2">
-        <v>-19366</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-19112.599999999999</v>
+      </c>
+      <c r="H37" s="1"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="O37" s="1"/>
+      <c r="P37" s="2"/>
+      <c r="Q37" s="2"/>
+      <c r="R37" s="2"/>
+      <c r="S37" s="2"/>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A38" s="1">
         <v>4099999.9999999995</v>
       </c>
       <c r="B38" s="2">
-        <v>18538.900000000001</v>
+        <v>26540</v>
       </c>
       <c r="C38" s="2">
-        <v>-89.238</v>
+        <v>-46.47</v>
       </c>
       <c r="D38" s="2">
-        <v>246.535</v>
+        <v>18279.2</v>
       </c>
       <c r="E38" s="2">
-        <v>-18537.3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-19241.8</v>
+      </c>
+      <c r="H38" s="1"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
+      <c r="O38" s="1"/>
+      <c r="P38" s="2"/>
+      <c r="Q38" s="2"/>
+      <c r="R38" s="2"/>
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A39" s="1">
         <v>4300000</v>
       </c>
       <c r="B39" s="2">
-        <v>17820.3</v>
+        <v>25880.7</v>
       </c>
       <c r="C39" s="2">
-        <v>-89.242999999999995</v>
+        <v>-48.106999999999999</v>
       </c>
       <c r="D39" s="2">
-        <v>235.38300000000001</v>
+        <v>17281.5</v>
       </c>
       <c r="E39" s="2">
-        <v>-17818.8</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-19265.400000000001</v>
+      </c>
+      <c r="H39" s="1"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+      <c r="O39" s="1"/>
+      <c r="P39" s="2"/>
+      <c r="Q39" s="2"/>
+      <c r="R39" s="2"/>
+      <c r="S39" s="2"/>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A40" s="1">
         <v>4400000</v>
       </c>
       <c r="B40" s="2">
-        <v>17320.2</v>
+        <v>25408.1</v>
       </c>
       <c r="C40" s="2">
-        <v>-89.453999999999994</v>
+        <v>-48.322000000000003</v>
       </c>
       <c r="D40" s="2">
-        <v>164.94399999999999</v>
+        <v>16895.099999999999</v>
       </c>
       <c r="E40" s="2">
-        <v>-17319.400000000001</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-18977</v>
+      </c>
+      <c r="H40" s="1"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
+      <c r="O40" s="1"/>
+      <c r="P40" s="2"/>
+      <c r="Q40" s="2"/>
+      <c r="R40" s="2"/>
+      <c r="S40" s="2"/>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A41" s="1">
         <v>4600000</v>
       </c>
       <c r="B41" s="2">
-        <v>16696.8</v>
+        <v>25214.799999999999</v>
       </c>
       <c r="C41" s="2">
-        <v>-89.290999999999997</v>
+        <v>-49.63</v>
       </c>
       <c r="D41" s="2">
-        <v>206.60400000000001</v>
+        <v>16332</v>
       </c>
       <c r="E41" s="2">
-        <v>-16695.5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-19210.7</v>
+      </c>
+      <c r="H41" s="1"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2"/>
+      <c r="L41" s="2"/>
+      <c r="O41" s="1"/>
+      <c r="P41" s="2"/>
+      <c r="Q41" s="2"/>
+      <c r="R41" s="2"/>
+      <c r="S41" s="2"/>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A42" s="1">
         <v>4800000</v>
       </c>
       <c r="B42" s="2">
-        <v>15896.7</v>
+        <v>24608.400000000001</v>
       </c>
       <c r="C42" s="2">
-        <v>-89.361000000000004</v>
+        <v>-50.612000000000002</v>
       </c>
       <c r="D42" s="2">
-        <v>177.20400000000001</v>
+        <v>15615.6</v>
       </c>
       <c r="E42" s="2">
-        <v>-15895.7</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-19019.099999999999</v>
+      </c>
+      <c r="H42" s="1"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
+      <c r="L42" s="2"/>
+      <c r="O42" s="1"/>
+      <c r="P42" s="2"/>
+      <c r="Q42" s="2"/>
+      <c r="R42" s="2"/>
+      <c r="S42" s="2"/>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A43" s="1">
         <v>5000000</v>
       </c>
       <c r="B43" s="2">
-        <v>15236.5</v>
+        <v>23603.3</v>
       </c>
       <c r="C43" s="2">
-        <v>-89.236999999999995</v>
+        <v>-51.744</v>
       </c>
       <c r="D43" s="2">
-        <v>202.90100000000001</v>
+        <v>14614.7</v>
       </c>
       <c r="E43" s="2">
-        <v>-15235.2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-18534.400000000001</v>
+      </c>
+      <c r="H43" s="1"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2"/>
+      <c r="L43" s="2"/>
+      <c r="O43" s="1"/>
+      <c r="P43" s="2"/>
+      <c r="Q43" s="2"/>
+      <c r="R43" s="2"/>
+      <c r="S43" s="2"/>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A44" s="1">
         <v>5200000</v>
       </c>
       <c r="B44" s="2">
-        <v>14704.9</v>
+        <v>23573.599999999999</v>
       </c>
       <c r="C44" s="2">
-        <v>-89.215999999999994</v>
+        <v>-52.345999999999997</v>
       </c>
       <c r="D44" s="2">
-        <v>201.11600000000001</v>
+        <v>14400.8</v>
       </c>
       <c r="E44" s="2">
-        <v>-14703.5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-18663.599999999999</v>
+      </c>
+      <c r="H44" s="1"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2"/>
+      <c r="L44" s="2"/>
+      <c r="O44" s="1"/>
+      <c r="P44" s="2"/>
+      <c r="Q44" s="2"/>
+      <c r="R44" s="2"/>
+      <c r="S44" s="2"/>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A45" s="1">
         <v>5400000</v>
       </c>
       <c r="B45" s="2">
-        <v>14271.5</v>
+        <v>22871.599999999999</v>
       </c>
       <c r="C45" s="2">
-        <v>-89.245000000000005</v>
+        <v>-53.212000000000003</v>
       </c>
       <c r="D45" s="2">
-        <v>188.12700000000001</v>
+        <v>13696.6</v>
       </c>
       <c r="E45" s="2">
-        <v>-14270.2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-18317</v>
+      </c>
+      <c r="H45" s="1"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="2"/>
+      <c r="K45" s="2"/>
+      <c r="L45" s="2"/>
+      <c r="O45" s="1"/>
+      <c r="P45" s="2"/>
+      <c r="Q45" s="2"/>
+      <c r="R45" s="2"/>
+      <c r="S45" s="2"/>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A46" s="1">
         <v>5600000</v>
       </c>
       <c r="B46" s="2">
-        <v>13754.2</v>
+        <v>22290.6</v>
       </c>
       <c r="C46" s="2">
-        <v>-89.179000000000002</v>
+        <v>-53.378</v>
       </c>
       <c r="D46" s="2">
-        <v>196.96</v>
+        <v>13297</v>
       </c>
       <c r="E46" s="2">
-        <v>-13752.8</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-17890.2</v>
+      </c>
+      <c r="H46" s="1"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="2"/>
+      <c r="K46" s="2"/>
+      <c r="L46" s="2"/>
+      <c r="O46" s="1"/>
+      <c r="P46" s="2"/>
+      <c r="Q46" s="2"/>
+      <c r="R46" s="2"/>
+      <c r="S46" s="2"/>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A47" s="1">
         <v>5900000</v>
       </c>
       <c r="B47" s="2">
-        <v>13048.2</v>
+        <v>21432.6</v>
       </c>
       <c r="C47" s="2">
-        <v>-89.167000000000002</v>
+        <v>-55.741</v>
       </c>
       <c r="D47" s="2">
-        <v>189.70099999999999</v>
+        <v>12065.3</v>
       </c>
       <c r="E47" s="2">
-        <v>-13046.8</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-17714</v>
+      </c>
+      <c r="H47" s="1"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="2"/>
+      <c r="K47" s="2"/>
+      <c r="L47" s="2"/>
+      <c r="O47" s="1"/>
+      <c r="P47" s="2"/>
+      <c r="Q47" s="2"/>
+      <c r="R47" s="2"/>
+      <c r="S47" s="2"/>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A48" s="1">
         <v>6100000</v>
       </c>
       <c r="B48" s="2">
-        <v>12696.4</v>
+        <v>21523</v>
       </c>
       <c r="C48" s="2">
-        <v>-89.376000000000005</v>
+        <v>-55.505000000000003</v>
       </c>
       <c r="D48" s="2">
-        <v>138.239</v>
+        <v>12189.3</v>
       </c>
       <c r="E48" s="2">
-        <v>-12695.7</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-17738.599999999999</v>
+      </c>
+      <c r="H48" s="1"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="2"/>
+      <c r="K48" s="2"/>
+      <c r="L48" s="2"/>
+      <c r="O48" s="1"/>
+      <c r="P48" s="2"/>
+      <c r="Q48" s="2"/>
+      <c r="R48" s="2"/>
+      <c r="S48" s="2"/>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A49" s="1">
         <v>6400000</v>
       </c>
       <c r="B49" s="2">
-        <v>12112.4</v>
+        <v>20788.400000000001</v>
       </c>
       <c r="C49" s="2">
-        <v>-89.319000000000003</v>
+        <v>-56.731999999999999</v>
       </c>
       <c r="D49" s="2">
-        <v>144.03</v>
+        <v>11403.7</v>
       </c>
       <c r="E49" s="2">
-        <v>-12111.6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-17381.400000000001</v>
+      </c>
+      <c r="H49" s="1"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="2"/>
+      <c r="K49" s="2"/>
+      <c r="L49" s="2"/>
+      <c r="O49" s="1"/>
+      <c r="P49" s="2"/>
+      <c r="Q49" s="2"/>
+      <c r="R49" s="2"/>
+      <c r="S49" s="2"/>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A50" s="1">
         <v>6600000</v>
       </c>
       <c r="B50" s="2">
-        <v>11746.8</v>
+        <v>20323.099999999999</v>
       </c>
       <c r="C50" s="2">
-        <v>-89.421000000000006</v>
+        <v>-57.151000000000003</v>
       </c>
       <c r="D50" s="2">
-        <v>118.747</v>
+        <v>11023.8</v>
       </c>
       <c r="E50" s="2">
-        <v>-11746.2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-17073.5</v>
+      </c>
+      <c r="H50" s="1"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="2"/>
+      <c r="K50" s="2"/>
+      <c r="L50" s="2"/>
+      <c r="O50" s="1"/>
+      <c r="P50" s="2"/>
+      <c r="Q50" s="2"/>
+      <c r="R50" s="2"/>
+      <c r="S50" s="2"/>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A51" s="1">
         <v>6900000</v>
       </c>
       <c r="B51" s="2">
-        <v>11236.9</v>
+        <v>19718.8</v>
       </c>
       <c r="C51" s="2">
-        <v>-89.284000000000006</v>
+        <v>-57.923000000000002</v>
       </c>
       <c r="D51" s="2">
-        <v>140.375</v>
+        <v>10472</v>
       </c>
       <c r="E51" s="2">
-        <v>-11236</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-16708.400000000001</v>
+      </c>
+      <c r="H51" s="1"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="2"/>
+      <c r="K51" s="2"/>
+      <c r="L51" s="2"/>
+      <c r="O51" s="1"/>
+      <c r="P51" s="2"/>
+      <c r="Q51" s="2"/>
+      <c r="R51" s="2"/>
+      <c r="S51" s="2"/>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A52" s="1">
         <v>7200000</v>
       </c>
       <c r="B52" s="2">
-        <v>10773</v>
+        <v>18961.2</v>
       </c>
       <c r="C52" s="2">
-        <v>-89.296999999999997</v>
+        <v>-59.718000000000004</v>
       </c>
       <c r="D52" s="2">
-        <v>132.21299999999999</v>
+        <v>9561.32</v>
       </c>
       <c r="E52" s="2">
-        <v>-10772.1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-16374</v>
+      </c>
+      <c r="H52" s="1"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="2"/>
+      <c r="K52" s="2"/>
+      <c r="L52" s="2"/>
+      <c r="O52" s="1"/>
+      <c r="P52" s="2"/>
+      <c r="Q52" s="2"/>
+      <c r="R52" s="2"/>
+      <c r="S52" s="2"/>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A53" s="1">
         <v>7500000</v>
       </c>
       <c r="B53" s="2">
-        <v>10331.5</v>
+        <v>18551.900000000001</v>
       </c>
       <c r="C53" s="2">
-        <v>-89.436000000000007</v>
+        <v>-60.16</v>
       </c>
       <c r="D53" s="2">
-        <v>101.78700000000001</v>
+        <v>9231.01</v>
       </c>
       <c r="E53" s="2">
-        <v>-10331</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-16092.2</v>
+      </c>
+      <c r="H53" s="1"/>
+      <c r="I53" s="2"/>
+      <c r="J53" s="2"/>
+      <c r="K53" s="2"/>
+      <c r="L53" s="2"/>
+      <c r="O53" s="1"/>
+      <c r="P53" s="2"/>
+      <c r="Q53" s="2"/>
+      <c r="R53" s="2"/>
+      <c r="S53" s="2"/>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A54" s="1">
         <v>7800000</v>
       </c>
       <c r="B54" s="2">
-        <v>9916.6299999999992</v>
+        <v>17796.900000000001</v>
       </c>
       <c r="C54" s="2">
-        <v>-89.347999999999999</v>
+        <v>-61.006999999999998</v>
       </c>
       <c r="D54" s="2">
-        <v>112.91200000000001</v>
+        <v>8626.25</v>
       </c>
       <c r="E54" s="2">
-        <v>-9915.99</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-15566.5</v>
+      </c>
+      <c r="H54" s="1"/>
+      <c r="I54" s="2"/>
+      <c r="J54" s="2"/>
+      <c r="K54" s="2"/>
+      <c r="L54" s="2"/>
+      <c r="O54" s="1"/>
+      <c r="P54" s="2"/>
+      <c r="Q54" s="2"/>
+      <c r="R54" s="2"/>
+      <c r="S54" s="2"/>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A55" s="1">
         <v>8100000</v>
       </c>
       <c r="B55" s="2">
-        <v>9539.02</v>
+        <v>17252.7</v>
       </c>
       <c r="C55" s="2">
-        <v>-89.236999999999995</v>
+        <v>-62.206000000000003</v>
       </c>
       <c r="D55" s="2">
-        <v>127.001</v>
+        <v>8044.75</v>
       </c>
       <c r="E55" s="2">
-        <v>-9538.18</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-15262.3</v>
+      </c>
+      <c r="H55" s="1"/>
+      <c r="I55" s="2"/>
+      <c r="J55" s="2"/>
+      <c r="K55" s="2"/>
+      <c r="L55" s="2"/>
+      <c r="O55" s="1"/>
+      <c r="P55" s="2"/>
+      <c r="Q55" s="2"/>
+      <c r="R55" s="2"/>
+      <c r="S55" s="2"/>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A56" s="1">
         <v>8400000</v>
       </c>
       <c r="B56" s="2">
-        <v>9209.5499999999993</v>
+        <v>16777.8</v>
       </c>
       <c r="C56" s="2">
-        <v>-89.239000000000004</v>
+        <v>-62.247</v>
       </c>
       <c r="D56" s="2">
-        <v>122.327</v>
+        <v>7812.67</v>
       </c>
       <c r="E56" s="2">
-        <v>-9208.74</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-14847.7</v>
+      </c>
+      <c r="H56" s="1"/>
+      <c r="I56" s="2"/>
+      <c r="J56" s="2"/>
+      <c r="K56" s="2"/>
+      <c r="L56" s="2"/>
+      <c r="O56" s="1"/>
+      <c r="P56" s="2"/>
+      <c r="Q56" s="2"/>
+      <c r="R56" s="2"/>
+      <c r="S56" s="2"/>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A57" s="1">
         <v>8800000</v>
       </c>
       <c r="B57" s="2">
-        <v>8767.1</v>
+        <v>16216.5</v>
       </c>
       <c r="C57" s="2">
-        <v>-89.388000000000005</v>
+        <v>-63.426000000000002</v>
       </c>
       <c r="D57" s="2">
-        <v>93.567300000000003</v>
+        <v>7254.47</v>
       </c>
       <c r="E57" s="2">
-        <v>-8766.6</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-14503.4</v>
+      </c>
+      <c r="H57" s="1"/>
+      <c r="I57" s="2"/>
+      <c r="J57" s="2"/>
+      <c r="K57" s="2"/>
+      <c r="L57" s="2"/>
+      <c r="O57" s="1"/>
+      <c r="P57" s="2"/>
+      <c r="Q57" s="2"/>
+      <c r="R57" s="2"/>
+      <c r="S57" s="2"/>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A58" s="1">
         <v>9100000</v>
       </c>
       <c r="B58" s="2">
-        <v>8473.49</v>
+        <v>15738.8</v>
       </c>
       <c r="C58" s="2">
-        <v>-89.331999999999994</v>
+        <v>-64.561000000000007</v>
       </c>
       <c r="D58" s="2">
-        <v>98.8459</v>
+        <v>6760.62</v>
       </c>
       <c r="E58" s="2">
-        <v>-8472.91</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-14212.8</v>
+      </c>
+      <c r="H58" s="1"/>
+      <c r="I58" s="2"/>
+      <c r="J58" s="2"/>
+      <c r="K58" s="2"/>
+      <c r="L58" s="2"/>
+      <c r="O58" s="1"/>
+      <c r="P58" s="2"/>
+      <c r="Q58" s="2"/>
+      <c r="R58" s="2"/>
+      <c r="S58" s="2"/>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A59" s="1">
         <v>9500000</v>
       </c>
       <c r="B59" s="2">
-        <v>8104.72</v>
+        <v>15088.9</v>
       </c>
       <c r="C59" s="2">
-        <v>-89.206999999999994</v>
+        <v>-65.007000000000005</v>
       </c>
       <c r="D59" s="2">
-        <v>112.232</v>
+        <v>6375.21</v>
       </c>
       <c r="E59" s="2">
-        <v>-8103.94</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-13676</v>
+      </c>
+      <c r="H59" s="1"/>
+      <c r="I59" s="2"/>
+      <c r="J59" s="2"/>
+      <c r="K59" s="2"/>
+      <c r="L59" s="2"/>
+      <c r="O59" s="1"/>
+      <c r="P59" s="2"/>
+      <c r="Q59" s="2"/>
+      <c r="R59" s="2"/>
+      <c r="S59" s="2"/>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A60" s="1">
         <v>9900000</v>
       </c>
       <c r="B60" s="2">
-        <v>7780.55</v>
+        <v>14669.4</v>
       </c>
       <c r="C60" s="2">
-        <v>-89.143000000000001</v>
+        <v>-66.119</v>
       </c>
       <c r="D60" s="2">
-        <v>116.336</v>
+        <v>5938.86</v>
       </c>
       <c r="E60" s="2">
-        <v>-7779.68</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-13413.5</v>
+      </c>
+      <c r="H60" s="1"/>
+      <c r="I60" s="2"/>
+      <c r="J60" s="2"/>
+      <c r="K60" s="2"/>
+      <c r="L60" s="2"/>
+      <c r="O60" s="1"/>
+      <c r="P60" s="2"/>
+      <c r="Q60" s="2"/>
+      <c r="R60" s="2"/>
+      <c r="S60" s="2"/>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A61" s="1">
         <v>10300000</v>
       </c>
       <c r="B61" s="2">
-        <v>7460.06</v>
+        <v>14082.3</v>
       </c>
       <c r="C61" s="2">
-        <v>-89.129000000000005</v>
+        <v>-66.927999999999997</v>
       </c>
       <c r="D61" s="2">
-        <v>113.42100000000001</v>
+        <v>5518.64</v>
       </c>
       <c r="E61" s="2">
-        <v>-7459.2</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-12955.9</v>
+      </c>
+      <c r="H61" s="1"/>
+      <c r="I61" s="2"/>
+      <c r="J61" s="2"/>
+      <c r="K61" s="2"/>
+      <c r="L61" s="2"/>
+      <c r="O61" s="1"/>
+      <c r="P61" s="2"/>
+      <c r="Q61" s="2"/>
+      <c r="R61" s="2"/>
+      <c r="S61" s="2"/>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A62" s="1">
         <v>10700000</v>
       </c>
       <c r="B62" s="2">
-        <v>7190.41</v>
+        <v>13646.2</v>
       </c>
       <c r="C62" s="2">
-        <v>-89.278000000000006</v>
+        <v>-67.563000000000002</v>
       </c>
       <c r="D62" s="2">
-        <v>90.570099999999996</v>
+        <v>5208.38</v>
       </c>
       <c r="E62" s="2">
-        <v>-7189.84</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-12613.2</v>
+      </c>
+      <c r="H62" s="1"/>
+      <c r="I62" s="2"/>
+      <c r="J62" s="2"/>
+      <c r="K62" s="2"/>
+      <c r="L62" s="2"/>
+      <c r="O62" s="1"/>
+      <c r="P62" s="2"/>
+      <c r="Q62" s="2"/>
+      <c r="R62" s="2"/>
+      <c r="S62" s="2"/>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A63" s="1">
         <v>11200000</v>
       </c>
       <c r="B63" s="2">
-        <v>6877.2</v>
+        <v>13124.4</v>
       </c>
       <c r="C63" s="2">
-        <v>-89.125</v>
+        <v>-68.218999999999994</v>
       </c>
       <c r="D63" s="2">
-        <v>104.96299999999999</v>
+        <v>4869.8599999999997</v>
       </c>
       <c r="E63" s="2">
-        <v>-6876.39</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-12187.4</v>
+      </c>
+      <c r="H63" s="1"/>
+      <c r="I63" s="2"/>
+      <c r="J63" s="2"/>
+      <c r="K63" s="2"/>
+      <c r="L63" s="2"/>
+      <c r="O63" s="1"/>
+      <c r="P63" s="2"/>
+      <c r="Q63" s="2"/>
+      <c r="R63" s="2"/>
+      <c r="S63" s="2"/>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A64" s="1">
         <v>11600000</v>
       </c>
       <c r="B64" s="2">
-        <v>6642.27</v>
+        <v>12696.6</v>
       </c>
       <c r="C64" s="2">
-        <v>-89.16</v>
+        <v>-69.046999999999997</v>
       </c>
       <c r="D64" s="2">
-        <v>97.392899999999997</v>
+        <v>4540.45</v>
       </c>
       <c r="E64" s="2">
-        <v>-6641.55</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-11857</v>
+      </c>
+      <c r="H64" s="1"/>
+      <c r="I64" s="2"/>
+      <c r="J64" s="2"/>
+      <c r="K64" s="2"/>
+      <c r="L64" s="2"/>
+      <c r="O64" s="1"/>
+      <c r="P64" s="2"/>
+      <c r="Q64" s="2"/>
+      <c r="R64" s="2"/>
+      <c r="S64" s="2"/>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A65" s="1">
         <v>12100000</v>
       </c>
       <c r="B65" s="2">
-        <v>6371.15</v>
+        <v>12280.9</v>
       </c>
       <c r="C65" s="2">
-        <v>-89.064999999999998</v>
+        <v>-69.426000000000002</v>
       </c>
       <c r="D65" s="2">
-        <v>103.926</v>
+        <v>4315.7</v>
       </c>
       <c r="E65" s="2">
-        <v>-6370.3</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-11497.6</v>
+      </c>
+      <c r="H65" s="1"/>
+      <c r="I65" s="2"/>
+      <c r="J65" s="2"/>
+      <c r="K65" s="2"/>
+      <c r="L65" s="2"/>
+      <c r="O65" s="1"/>
+      <c r="P65" s="2"/>
+      <c r="Q65" s="2"/>
+      <c r="R65" s="2"/>
+      <c r="S65" s="2"/>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A66" s="1">
         <v>12600000</v>
       </c>
       <c r="B66" s="2">
-        <v>6126.75</v>
+        <v>11921.3</v>
       </c>
       <c r="C66" s="2">
-        <v>-89.435000000000002</v>
+        <v>-70.566999999999993</v>
       </c>
       <c r="D66" s="2">
-        <v>60.423000000000002</v>
+        <v>3966.25</v>
       </c>
       <c r="E66" s="2">
-        <v>-6126.45</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-11242.2</v>
+      </c>
+      <c r="H66" s="1"/>
+      <c r="I66" s="2"/>
+      <c r="J66" s="2"/>
+      <c r="K66" s="2"/>
+      <c r="L66" s="2"/>
+      <c r="O66" s="1"/>
+      <c r="P66" s="2"/>
+      <c r="Q66" s="2"/>
+      <c r="R66" s="2"/>
+      <c r="S66" s="2"/>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A67" s="1">
         <v>13100000</v>
       </c>
       <c r="B67" s="2">
-        <v>5879.36</v>
+        <v>11553.8</v>
       </c>
       <c r="C67" s="2">
-        <v>-89.635000000000005</v>
+        <v>-71.628</v>
       </c>
       <c r="D67" s="2">
-        <v>37.468600000000002</v>
+        <v>3641.62</v>
       </c>
       <c r="E67" s="2">
-        <v>-5879.24</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-10964.9</v>
+      </c>
+      <c r="H67" s="1"/>
+      <c r="I67" s="2"/>
+      <c r="J67" s="2"/>
+      <c r="K67" s="2"/>
+      <c r="L67" s="2"/>
+      <c r="O67" s="1"/>
+      <c r="P67" s="2"/>
+      <c r="Q67" s="2"/>
+      <c r="R67" s="2"/>
+      <c r="S67" s="2"/>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A68" s="1">
         <v>13700000</v>
       </c>
       <c r="B68" s="2">
-        <v>5623.6</v>
+        <v>11043.4</v>
       </c>
       <c r="C68" s="2">
-        <v>-89.679000000000002</v>
+        <v>-72.509</v>
       </c>
       <c r="D68" s="2">
-        <v>31.458400000000001</v>
+        <v>3319.19</v>
       </c>
       <c r="E68" s="2">
-        <v>-5623.52</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-10532.8</v>
+      </c>
+      <c r="H68" s="1"/>
+      <c r="I68" s="2"/>
+      <c r="J68" s="2"/>
+      <c r="K68" s="2"/>
+      <c r="L68" s="2"/>
+      <c r="O68" s="1"/>
+      <c r="P68" s="2"/>
+      <c r="Q68" s="2"/>
+      <c r="R68" s="2"/>
+      <c r="S68" s="2"/>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A69" s="1">
         <v>14200000</v>
       </c>
       <c r="B69" s="2">
-        <v>5425.98</v>
+        <v>10669.2</v>
       </c>
       <c r="C69" s="2">
-        <v>-89.813999999999993</v>
+        <v>-73.302999999999997</v>
       </c>
       <c r="D69" s="2">
-        <v>17.616599999999998</v>
+        <v>3065.29</v>
       </c>
       <c r="E69" s="2">
-        <v>-5425.95</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-10219.4</v>
+      </c>
+      <c r="H69" s="1"/>
+      <c r="I69" s="2"/>
+      <c r="J69" s="2"/>
+      <c r="K69" s="2"/>
+      <c r="L69" s="2"/>
+      <c r="O69" s="1"/>
+      <c r="P69" s="2"/>
+      <c r="Q69" s="2"/>
+      <c r="R69" s="2"/>
+      <c r="S69" s="2"/>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A70" s="1">
         <v>14800000</v>
       </c>
       <c r="B70" s="2">
-        <v>5206.49</v>
+        <v>10312.200000000001</v>
       </c>
       <c r="C70" s="2">
-        <v>-89.820999999999998</v>
+        <v>-73.841999999999999</v>
       </c>
       <c r="D70" s="2">
-        <v>16.227799999999998</v>
+        <v>2869.75</v>
       </c>
       <c r="E70" s="2">
-        <v>-5206.46</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-9904.7999999999993</v>
+      </c>
+      <c r="H70" s="1"/>
+      <c r="I70" s="2"/>
+      <c r="J70" s="2"/>
+      <c r="K70" s="2"/>
+      <c r="L70" s="2"/>
+      <c r="O70" s="1"/>
+      <c r="P70" s="2"/>
+      <c r="Q70" s="2"/>
+      <c r="R70" s="2"/>
+      <c r="S70" s="2"/>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A71" s="1">
         <v>15400000</v>
       </c>
       <c r="B71" s="2">
-        <v>4999.3100000000004</v>
+        <v>9923.15</v>
       </c>
       <c r="C71" s="2">
-        <v>-89.852000000000004</v>
+        <v>-74.572000000000003</v>
       </c>
       <c r="D71" s="2">
-        <v>12.936299999999999</v>
+        <v>2639.77</v>
       </c>
       <c r="E71" s="2">
-        <v>-4999.29</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-9565.59</v>
+      </c>
+      <c r="H71" s="1"/>
+      <c r="I71" s="2"/>
+      <c r="J71" s="2"/>
+      <c r="K71" s="2"/>
+      <c r="L71" s="2"/>
+      <c r="O71" s="1"/>
+      <c r="P71" s="2"/>
+      <c r="Q71" s="2"/>
+      <c r="R71" s="2"/>
+      <c r="S71" s="2"/>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A72" s="1">
         <v>16100000.000000002</v>
       </c>
       <c r="B72" s="2">
-        <v>4787.1899999999996</v>
+        <v>9560.2800000000007</v>
       </c>
       <c r="C72" s="2">
-        <v>-89.834999999999994</v>
+        <v>-74.762</v>
       </c>
       <c r="D72" s="2">
-        <v>13.8264</v>
+        <v>2512.67</v>
       </c>
       <c r="E72" s="2">
-        <v>-4787.17</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-9224.18</v>
+      </c>
+      <c r="H72" s="1"/>
+      <c r="I72" s="2"/>
+      <c r="J72" s="2"/>
+      <c r="K72" s="2"/>
+      <c r="L72" s="2"/>
+      <c r="O72" s="1"/>
+      <c r="P72" s="2"/>
+      <c r="Q72" s="2"/>
+      <c r="R72" s="2"/>
+      <c r="S72" s="2"/>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A73" s="1">
         <v>16700000</v>
       </c>
       <c r="B73" s="2">
-        <v>4616.87</v>
+        <v>9264.1200000000008</v>
       </c>
       <c r="C73" s="2">
-        <v>-89.698999999999998</v>
+        <v>-75.149000000000001</v>
       </c>
       <c r="D73" s="2">
-        <v>24.2818</v>
+        <v>2374.41</v>
       </c>
       <c r="E73" s="2">
-        <v>-4616.8</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-8954.66</v>
+      </c>
+      <c r="H73" s="1"/>
+      <c r="I73" s="2"/>
+      <c r="J73" s="2"/>
+      <c r="K73" s="2"/>
+      <c r="L73" s="2"/>
+      <c r="O73" s="1"/>
+      <c r="P73" s="2"/>
+      <c r="Q73" s="2"/>
+      <c r="R73" s="2"/>
+      <c r="S73" s="2"/>
+    </row>
+    <row r="74" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A74" s="1">
         <v>17400000</v>
       </c>
       <c r="B74" s="2">
-        <v>4434.55</v>
+        <v>8868.65</v>
       </c>
       <c r="C74" s="2">
-        <v>-89.525000000000006</v>
+        <v>-75.546999999999997</v>
       </c>
       <c r="D74" s="2">
-        <v>36.767499999999998</v>
+        <v>2213.4899999999998</v>
       </c>
       <c r="E74" s="2">
-        <v>-4434.3999999999996</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-8587.98</v>
+      </c>
+      <c r="H74" s="1"/>
+      <c r="I74" s="2"/>
+      <c r="J74" s="2"/>
+      <c r="K74" s="2"/>
+      <c r="L74" s="2"/>
+      <c r="O74" s="1"/>
+      <c r="P74" s="2"/>
+      <c r="Q74" s="2"/>
+      <c r="R74" s="2"/>
+      <c r="S74" s="2"/>
+    </row>
+    <row r="75" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A75" s="1">
         <v>18100000</v>
       </c>
       <c r="B75" s="2">
-        <v>4264.26</v>
+        <v>8580.94</v>
       </c>
       <c r="C75" s="2">
-        <v>-89.38</v>
+        <v>-75.484999999999999</v>
       </c>
       <c r="D75" s="2">
-        <v>46.162500000000001</v>
+        <v>2150.71</v>
       </c>
       <c r="E75" s="2">
-        <v>-4264.01</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-8307.0400000000009</v>
+      </c>
+      <c r="H75" s="1"/>
+      <c r="I75" s="2"/>
+      <c r="J75" s="2"/>
+      <c r="K75" s="2"/>
+      <c r="L75" s="2"/>
+      <c r="O75" s="1"/>
+      <c r="P75" s="2"/>
+      <c r="Q75" s="2"/>
+      <c r="R75" s="2"/>
+      <c r="S75" s="2"/>
+    </row>
+    <row r="76" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A76" s="1">
         <v>18900000</v>
       </c>
       <c r="B76" s="2">
-        <v>4091.86</v>
+        <v>8259.58</v>
       </c>
       <c r="C76" s="2">
-        <v>-89.194000000000003</v>
+        <v>-75.623999999999995</v>
       </c>
       <c r="D76" s="2">
-        <v>57.551699999999997</v>
+        <v>2050.77</v>
       </c>
       <c r="E76" s="2">
-        <v>-4091.45</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-8000.94</v>
+      </c>
+      <c r="H76" s="1"/>
+      <c r="I76" s="2"/>
+      <c r="J76" s="2"/>
+      <c r="K76" s="2"/>
+      <c r="L76" s="2"/>
+      <c r="O76" s="1"/>
+      <c r="P76" s="2"/>
+      <c r="Q76" s="2"/>
+      <c r="R76" s="2"/>
+      <c r="S76" s="2"/>
+    </row>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A77" s="1">
         <v>19600000</v>
       </c>
       <c r="B77" s="2">
-        <v>3944.02</v>
+        <v>7985.78</v>
       </c>
       <c r="C77" s="2">
-        <v>-88.936000000000007</v>
+        <v>-75.415000000000006</v>
       </c>
       <c r="D77" s="2">
-        <v>73.230099999999993</v>
+        <v>2010.98</v>
       </c>
       <c r="E77" s="2">
-        <v>-3943.34</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-7728.43</v>
+      </c>
+      <c r="H77" s="1"/>
+      <c r="I77" s="2"/>
+      <c r="J77" s="2"/>
+      <c r="K77" s="2"/>
+      <c r="L77" s="2"/>
+      <c r="O77" s="1"/>
+      <c r="P77" s="2"/>
+      <c r="Q77" s="2"/>
+      <c r="R77" s="2"/>
+      <c r="S77" s="2"/>
+    </row>
+    <row r="78" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A78" s="1">
         <v>20400000</v>
       </c>
       <c r="B78" s="2">
-        <v>3787.48</v>
+        <v>7680.87</v>
       </c>
       <c r="C78" s="2">
-        <v>-88.875</v>
+        <v>-76.091999999999999</v>
       </c>
       <c r="D78" s="2">
-        <v>74.366500000000002</v>
+        <v>1846.17</v>
       </c>
       <c r="E78" s="2">
-        <v>-3786.75</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-7455.7</v>
+      </c>
+      <c r="H78" s="1"/>
+      <c r="I78" s="2"/>
+      <c r="J78" s="2"/>
+      <c r="K78" s="2"/>
+      <c r="L78" s="2"/>
+      <c r="O78" s="1"/>
+      <c r="P78" s="2"/>
+      <c r="Q78" s="2"/>
+      <c r="R78" s="2"/>
+      <c r="S78" s="2"/>
+    </row>
+    <row r="79" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A79" s="1">
         <v>21300000</v>
       </c>
       <c r="B79" s="2">
-        <v>3631.17</v>
+        <v>7353.67</v>
       </c>
       <c r="C79" s="2">
-        <v>-89.106999999999999</v>
+        <v>-76.751000000000005</v>
       </c>
       <c r="D79" s="2">
-        <v>56.581699999999998</v>
+        <v>1685.39</v>
       </c>
       <c r="E79" s="2">
-        <v>-3630.73</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-7157.92</v>
+      </c>
+      <c r="H79" s="1"/>
+      <c r="I79" s="2"/>
+      <c r="J79" s="2"/>
+      <c r="K79" s="2"/>
+      <c r="L79" s="2"/>
+      <c r="O79" s="1"/>
+      <c r="P79" s="2"/>
+      <c r="Q79" s="2"/>
+      <c r="R79" s="2"/>
+      <c r="S79" s="2"/>
+    </row>
+    <row r="80" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A80" s="1">
         <v>22200000</v>
       </c>
       <c r="B80" s="2">
-        <v>3484.07</v>
+        <v>7091.3</v>
       </c>
       <c r="C80" s="2">
-        <v>-89.233000000000004</v>
+        <v>-77.551000000000002</v>
       </c>
       <c r="D80" s="2">
-        <v>46.654400000000003</v>
+        <v>1528.69</v>
       </c>
       <c r="E80" s="2">
-        <v>-3483.76</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-6924.57</v>
+      </c>
+      <c r="H80" s="1"/>
+      <c r="I80" s="2"/>
+      <c r="J80" s="2"/>
+      <c r="K80" s="2"/>
+      <c r="L80" s="2"/>
+      <c r="O80" s="1"/>
+      <c r="P80" s="2"/>
+      <c r="Q80" s="2"/>
+      <c r="R80" s="2"/>
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A81" s="1">
         <v>23100000</v>
       </c>
       <c r="B81" s="2">
-        <v>3348.09</v>
+        <v>6826.4</v>
       </c>
       <c r="C81" s="2">
-        <v>-89.363</v>
+        <v>-78.067999999999998</v>
       </c>
       <c r="D81" s="2">
-        <v>37.215499999999999</v>
+        <v>1411.38</v>
       </c>
       <c r="E81" s="2">
-        <v>-3347.88</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-6678.91</v>
+      </c>
+      <c r="H81" s="1"/>
+      <c r="I81" s="2"/>
+      <c r="J81" s="2"/>
+      <c r="K81" s="2"/>
+      <c r="L81" s="2"/>
+      <c r="O81" s="1"/>
+      <c r="P81" s="2"/>
+      <c r="Q81" s="2"/>
+      <c r="R81" s="2"/>
+      <c r="S81" s="2"/>
+    </row>
+    <row r="82" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A82" s="1">
         <v>24000000</v>
       </c>
       <c r="B82" s="2">
-        <v>3222.93</v>
+        <v>6600.35</v>
       </c>
       <c r="C82" s="2">
-        <v>-89.387</v>
+        <v>-78.409000000000006</v>
       </c>
       <c r="D82" s="2">
-        <v>34.508200000000002</v>
+        <v>1326.15</v>
       </c>
       <c r="E82" s="2">
-        <v>-3222.74</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-6465.75</v>
+      </c>
+      <c r="H82" s="1"/>
+      <c r="I82" s="2"/>
+      <c r="J82" s="2"/>
+      <c r="K82" s="2"/>
+      <c r="L82" s="2"/>
+      <c r="O82" s="1"/>
+      <c r="P82" s="2"/>
+      <c r="Q82" s="2"/>
+      <c r="R82" s="2"/>
+      <c r="S82" s="2"/>
+    </row>
+    <row r="83" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A83" s="1">
         <v>25000000</v>
       </c>
       <c r="B83" s="2">
-        <v>3096.17</v>
+        <v>6351.35</v>
       </c>
       <c r="C83" s="2">
-        <v>-89.272999999999996</v>
+        <v>-78.638999999999996</v>
       </c>
       <c r="D83" s="2">
-        <v>39.286900000000003</v>
+        <v>1251.1500000000001</v>
       </c>
       <c r="E83" s="2">
-        <v>-3095.92</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-6226.89</v>
+      </c>
+      <c r="H83" s="1"/>
+      <c r="I83" s="2"/>
+      <c r="J83" s="2"/>
+      <c r="K83" s="2"/>
+      <c r="L83" s="2"/>
+      <c r="O83" s="1"/>
+      <c r="P83" s="2"/>
+      <c r="Q83" s="2"/>
+      <c r="R83" s="2"/>
+      <c r="S83" s="2"/>
+    </row>
+    <row r="84" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A84" s="1">
         <v>26000000</v>
       </c>
       <c r="B84" s="2">
-        <v>2978.25</v>
+        <v>6130.93</v>
       </c>
       <c r="C84" s="2">
-        <v>-89.244</v>
+        <v>-78.820999999999998</v>
       </c>
       <c r="D84" s="2">
-        <v>39.304000000000002</v>
+        <v>1188.6099999999999</v>
       </c>
       <c r="E84" s="2">
-        <v>-2977.99</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-6014.61</v>
+      </c>
+      <c r="H84" s="1"/>
+      <c r="I84" s="2"/>
+      <c r="J84" s="2"/>
+      <c r="K84" s="2"/>
+      <c r="L84" s="2"/>
+      <c r="O84" s="1"/>
+      <c r="P84" s="2"/>
+      <c r="Q84" s="2"/>
+      <c r="R84" s="2"/>
+      <c r="S84" s="2"/>
+    </row>
+    <row r="85" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A85" s="1">
         <v>27100000</v>
       </c>
       <c r="B85" s="2">
-        <v>2858.48</v>
+        <v>5888.14</v>
       </c>
       <c r="C85" s="2">
-        <v>-89.081999999999994</v>
+        <v>-78.977999999999994</v>
       </c>
       <c r="D85" s="2">
-        <v>45.814300000000003</v>
+        <v>1125.77</v>
       </c>
       <c r="E85" s="2">
-        <v>-2858.12</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-5779.52</v>
+      </c>
+      <c r="H85" s="1"/>
+      <c r="I85" s="2"/>
+      <c r="J85" s="2"/>
+      <c r="K85" s="2"/>
+      <c r="L85" s="2"/>
+      <c r="O85" s="1"/>
+      <c r="P85" s="2"/>
+      <c r="Q85" s="2"/>
+      <c r="R85" s="2"/>
+      <c r="S85" s="2"/>
+    </row>
+    <row r="86" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A86" s="1">
         <v>28200000</v>
       </c>
       <c r="B86" s="2">
-        <v>2745.71</v>
+        <v>5638.78</v>
       </c>
       <c r="C86" s="2">
-        <v>-88.879000000000005</v>
+        <v>-78.921000000000006</v>
       </c>
       <c r="D86" s="2">
-        <v>53.711199999999998</v>
+        <v>1083.51</v>
       </c>
       <c r="E86" s="2">
-        <v>-2745.18</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-5533.7</v>
+      </c>
+      <c r="H86" s="1"/>
+      <c r="I86" s="2"/>
+      <c r="J86" s="2"/>
+      <c r="K86" s="2"/>
+      <c r="L86" s="2"/>
+      <c r="O86" s="1"/>
+      <c r="P86" s="2"/>
+      <c r="Q86" s="2"/>
+      <c r="R86" s="2"/>
+      <c r="S86" s="2"/>
+    </row>
+    <row r="87" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A87" s="1">
         <v>29400000</v>
       </c>
       <c r="B87" s="2">
-        <v>2633.26</v>
+        <v>5406.59</v>
       </c>
       <c r="C87" s="2">
-        <v>-88.528999999999996</v>
+        <v>-78.575999999999993</v>
       </c>
       <c r="D87" s="2">
-        <v>67.583100000000002</v>
+        <v>1070.8900000000001</v>
       </c>
       <c r="E87" s="2">
-        <v>-2632.4</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-5299.48</v>
+      </c>
+      <c r="H87" s="1"/>
+      <c r="I87" s="2"/>
+      <c r="J87" s="2"/>
+      <c r="K87" s="2"/>
+      <c r="L87" s="2"/>
+      <c r="O87" s="1"/>
+      <c r="P87" s="2"/>
+      <c r="Q87" s="2"/>
+      <c r="R87" s="2"/>
+      <c r="S87" s="2"/>
+    </row>
+    <row r="88" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A88" s="1">
         <v>30600000</v>
       </c>
       <c r="B88" s="2">
-        <v>2525.31</v>
+        <v>5187.0200000000004</v>
       </c>
       <c r="C88" s="2">
-        <v>-88.429000000000002</v>
+        <v>-78.8</v>
       </c>
       <c r="D88" s="2">
-        <v>69.246799999999993</v>
+        <v>1007.48</v>
       </c>
       <c r="E88" s="2">
-        <v>-2524.36</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-5088.24</v>
+      </c>
+      <c r="H88" s="1"/>
+      <c r="I88" s="2"/>
+      <c r="J88" s="2"/>
+      <c r="K88" s="2"/>
+      <c r="L88" s="2"/>
+      <c r="O88" s="1"/>
+      <c r="P88" s="2"/>
+      <c r="Q88" s="2"/>
+      <c r="R88" s="2"/>
+      <c r="S88" s="2"/>
+    </row>
+    <row r="89" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A89" s="1">
         <v>31800000</v>
       </c>
       <c r="B89" s="2">
-        <v>2429.15</v>
+        <v>5001.45</v>
       </c>
       <c r="C89" s="2">
-        <v>-88.543000000000006</v>
+        <v>-79.138999999999996</v>
       </c>
       <c r="D89" s="2">
-        <v>61.774999999999999</v>
+        <v>942.44299999999998</v>
       </c>
       <c r="E89" s="2">
-        <v>-2428.37</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-4911.8599999999997</v>
+      </c>
+      <c r="H89" s="1"/>
+      <c r="I89" s="2"/>
+      <c r="J89" s="2"/>
+      <c r="K89" s="2"/>
+      <c r="L89" s="2"/>
+      <c r="O89" s="1"/>
+      <c r="P89" s="2"/>
+      <c r="Q89" s="2"/>
+      <c r="R89" s="2"/>
+      <c r="S89" s="2"/>
+    </row>
+    <row r="90" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A90" s="1">
         <v>33100000</v>
       </c>
       <c r="B90" s="2">
-        <v>2336.44</v>
+        <v>4833</v>
       </c>
       <c r="C90" s="2">
-        <v>-88.613</v>
+        <v>-79.713999999999999</v>
       </c>
       <c r="D90" s="2">
-        <v>56.542200000000001</v>
+        <v>862.97199999999998</v>
       </c>
       <c r="E90" s="2">
-        <v>-2335.75</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-4755.33</v>
+      </c>
+      <c r="H90" s="1"/>
+      <c r="I90" s="2"/>
+      <c r="J90" s="2"/>
+      <c r="K90" s="2"/>
+      <c r="L90" s="2"/>
+      <c r="O90" s="1"/>
+      <c r="P90" s="2"/>
+      <c r="Q90" s="2"/>
+      <c r="R90" s="2"/>
+      <c r="S90" s="2"/>
+    </row>
+    <row r="91" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A91" s="1">
         <v>34500000</v>
       </c>
       <c r="B91" s="2">
-        <v>2243.5</v>
+        <v>4639.49</v>
       </c>
       <c r="C91" s="2">
-        <v>-88.644999999999996</v>
+        <v>-79.997</v>
       </c>
       <c r="D91" s="2">
-        <v>53.069600000000001</v>
+        <v>805.84400000000005</v>
       </c>
       <c r="E91" s="2">
-        <v>-2242.87</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-4568.97</v>
+      </c>
+      <c r="H91" s="1"/>
+      <c r="I91" s="2"/>
+      <c r="J91" s="2"/>
+      <c r="K91" s="2"/>
+      <c r="L91" s="2"/>
+      <c r="O91" s="1"/>
+      <c r="P91" s="2"/>
+      <c r="Q91" s="2"/>
+      <c r="R91" s="2"/>
+      <c r="S91" s="2"/>
+    </row>
+    <row r="92" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A92" s="1">
         <v>35900000</v>
       </c>
       <c r="B92" s="2">
-        <v>2155.73</v>
+        <v>4467.3900000000003</v>
       </c>
       <c r="C92" s="2">
-        <v>-88.644000000000005</v>
+        <v>-80.122</v>
       </c>
       <c r="D92" s="2">
-        <v>51.031599999999997</v>
+        <v>766.36900000000003</v>
       </c>
       <c r="E92" s="2">
-        <v>-2155.13</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-4401.17</v>
+      </c>
+      <c r="H92" s="1"/>
+      <c r="I92" s="2"/>
+      <c r="J92" s="2"/>
+      <c r="K92" s="2"/>
+      <c r="L92" s="2"/>
+      <c r="O92" s="1"/>
+      <c r="P92" s="2"/>
+      <c r="Q92" s="2"/>
+      <c r="R92" s="2"/>
+      <c r="S92" s="2"/>
+    </row>
+    <row r="93" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A93" s="1">
         <v>37400000</v>
       </c>
       <c r="B93" s="2">
-        <v>2068.89</v>
+        <v>4279.2299999999996</v>
       </c>
       <c r="C93" s="2">
-        <v>-88.429000000000002</v>
+        <v>-80.009</v>
       </c>
       <c r="D93" s="2">
-        <v>56.7318</v>
+        <v>742.40099999999995</v>
       </c>
       <c r="E93" s="2">
-        <v>-2068.12</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-4214.34</v>
+      </c>
+      <c r="H93" s="1"/>
+      <c r="I93" s="2"/>
+      <c r="J93" s="2"/>
+      <c r="K93" s="2"/>
+      <c r="L93" s="2"/>
+      <c r="O93" s="1"/>
+      <c r="P93" s="2"/>
+      <c r="Q93" s="2"/>
+      <c r="R93" s="2"/>
+      <c r="S93" s="2"/>
+    </row>
+    <row r="94" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A94" s="1">
         <v>38900000</v>
       </c>
       <c r="B94" s="2">
-        <v>1989.8</v>
+        <v>4110.26</v>
       </c>
       <c r="C94" s="2">
-        <v>-88.096000000000004</v>
+        <v>-79.584000000000003</v>
       </c>
       <c r="D94" s="2">
-        <v>66.104200000000006</v>
+        <v>743.08699999999999</v>
       </c>
       <c r="E94" s="2">
-        <v>-1988.7</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-4042.53</v>
+      </c>
+      <c r="H94" s="1"/>
+      <c r="I94" s="2"/>
+      <c r="J94" s="2"/>
+      <c r="K94" s="2"/>
+      <c r="L94" s="2"/>
+      <c r="O94" s="1"/>
+      <c r="P94" s="2"/>
+      <c r="Q94" s="2"/>
+      <c r="R94" s="2"/>
+      <c r="S94" s="2"/>
+    </row>
+    <row r="95" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A95" s="1">
         <v>40500000</v>
       </c>
       <c r="B95" s="2">
-        <v>1910.17</v>
+        <v>3954.84</v>
       </c>
       <c r="C95" s="2">
-        <v>-87.893000000000001</v>
+        <v>-79.444999999999993</v>
       </c>
       <c r="D95" s="2">
-        <v>70.230599999999995</v>
+        <v>724.42399999999998</v>
       </c>
       <c r="E95" s="2">
-        <v>-1908.88</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-3887.93</v>
+      </c>
+      <c r="H95" s="1"/>
+      <c r="I95" s="2"/>
+      <c r="J95" s="2"/>
+      <c r="K95" s="2"/>
+      <c r="L95" s="2"/>
+      <c r="O95" s="1"/>
+      <c r="P95" s="2"/>
+      <c r="Q95" s="2"/>
+      <c r="R95" s="2"/>
+      <c r="S95" s="2"/>
+    </row>
+    <row r="96" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A96" s="1">
         <v>42200000</v>
       </c>
       <c r="B96" s="2">
-        <v>1831.88</v>
+        <v>3797.97</v>
       </c>
       <c r="C96" s="2">
-        <v>-87.980999999999995</v>
+        <v>-79.92</v>
       </c>
       <c r="D96" s="2">
-        <v>64.527600000000007</v>
+        <v>664.75699999999995</v>
       </c>
       <c r="E96" s="2">
-        <v>-1830.74</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-3739.34</v>
+      </c>
+      <c r="H96" s="1"/>
+      <c r="I96" s="2"/>
+      <c r="J96" s="2"/>
+      <c r="K96" s="2"/>
+      <c r="L96" s="2"/>
+      <c r="O96" s="1"/>
+      <c r="P96" s="2"/>
+      <c r="Q96" s="2"/>
+      <c r="R96" s="2"/>
+      <c r="S96" s="2"/>
+    </row>
+    <row r="97" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A97" s="1">
         <v>43900000</v>
       </c>
       <c r="B97" s="2">
-        <v>1762.03</v>
+        <v>3654.26</v>
       </c>
       <c r="C97" s="2">
-        <v>-87.960999999999999</v>
+        <v>-80.102999999999994</v>
       </c>
       <c r="D97" s="2">
-        <v>62.6877</v>
+        <v>628.08100000000002</v>
       </c>
       <c r="E97" s="2">
-        <v>-1760.92</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-3599.88</v>
+      </c>
+      <c r="H97" s="1"/>
+      <c r="I97" s="2"/>
+      <c r="J97" s="2"/>
+      <c r="K97" s="2"/>
+      <c r="L97" s="2"/>
+      <c r="O97" s="1"/>
+      <c r="P97" s="2"/>
+      <c r="Q97" s="2"/>
+      <c r="R97" s="2"/>
+      <c r="S97" s="2"/>
+    </row>
+    <row r="98" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A98" s="1">
         <v>45700000</v>
       </c>
       <c r="B98" s="2">
-        <v>1693.99</v>
+        <v>3515.9</v>
       </c>
       <c r="C98" s="2">
-        <v>-87.834000000000003</v>
+        <v>-80.105000000000004</v>
       </c>
       <c r="D98" s="2">
-        <v>64.038799999999995</v>
+        <v>604.16300000000001</v>
       </c>
       <c r="E98" s="2">
-        <v>-1692.78</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-3463.6</v>
+      </c>
+      <c r="H98" s="1"/>
+      <c r="I98" s="2"/>
+      <c r="J98" s="2"/>
+      <c r="K98" s="2"/>
+      <c r="L98" s="2"/>
+      <c r="O98" s="1"/>
+      <c r="P98" s="2"/>
+      <c r="Q98" s="2"/>
+      <c r="R98" s="2"/>
+      <c r="S98" s="2"/>
+    </row>
+    <row r="99" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A99" s="1">
         <v>47600000</v>
       </c>
       <c r="B99" s="2">
-        <v>1628.17</v>
+        <v>3382.99</v>
       </c>
       <c r="C99" s="2">
-        <v>-87.644000000000005</v>
+        <v>-79.864999999999995</v>
       </c>
       <c r="D99" s="2">
-        <v>66.938100000000006</v>
+        <v>595.32399999999996</v>
       </c>
       <c r="E99" s="2">
-        <v>-1626.8</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-3330.2</v>
+      </c>
+      <c r="H99" s="1"/>
+      <c r="I99" s="2"/>
+      <c r="J99" s="2"/>
+      <c r="K99" s="2"/>
+      <c r="L99" s="2"/>
+      <c r="O99" s="1"/>
+      <c r="P99" s="2"/>
+      <c r="Q99" s="2"/>
+      <c r="R99" s="2"/>
+      <c r="S99" s="2"/>
+    </row>
+    <row r="100" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A100" s="1">
         <v>49500000</v>
       </c>
       <c r="B100" s="2">
-        <v>1565.53</v>
+        <v>3254</v>
       </c>
       <c r="C100" s="2">
-        <v>-87.372</v>
+        <v>-79.548000000000002</v>
       </c>
       <c r="D100" s="2">
-        <v>71.7821</v>
+        <v>590.33399999999995</v>
       </c>
       <c r="E100" s="2">
-        <v>-1563.89</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-3200.01</v>
+      </c>
+      <c r="H100" s="1"/>
+      <c r="I100" s="2"/>
+      <c r="J100" s="2"/>
+      <c r="K100" s="2"/>
+      <c r="L100" s="2"/>
+      <c r="O100" s="1"/>
+      <c r="P100" s="2"/>
+      <c r="Q100" s="2"/>
+      <c r="R100" s="2"/>
+      <c r="S100" s="2"/>
+    </row>
+    <row r="101" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A101" s="1">
         <v>51600000</v>
       </c>
       <c r="B101" s="2">
-        <v>1496.24</v>
+        <v>3094.84</v>
       </c>
       <c r="C101" s="2">
-        <v>-87.704999999999998</v>
+        <v>-80.325000000000003</v>
       </c>
       <c r="D101" s="2">
-        <v>59.9056</v>
+        <v>520.09100000000001</v>
       </c>
       <c r="E101" s="2">
-        <v>-1495.04</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-3050.83</v>
+      </c>
+      <c r="H101" s="1"/>
+      <c r="I101" s="2"/>
+      <c r="J101" s="2"/>
+      <c r="K101" s="2"/>
+      <c r="L101" s="2"/>
+      <c r="O101" s="1"/>
+      <c r="P101" s="2"/>
+      <c r="Q101" s="2"/>
+      <c r="R101" s="2"/>
+      <c r="S101" s="2"/>
+    </row>
+    <row r="102" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A102" s="1">
         <v>53700000</v>
       </c>
       <c r="B102" s="2">
-        <v>1430.35</v>
+        <v>2956.27</v>
       </c>
       <c r="C102" s="2">
-        <v>-87.87</v>
+        <v>-81.010000000000005</v>
       </c>
       <c r="D102" s="2">
-        <v>53.170299999999997</v>
+        <v>461.97</v>
       </c>
       <c r="E102" s="2">
-        <v>-1429.36</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-2919.95</v>
+      </c>
+      <c r="H102" s="1"/>
+      <c r="I102" s="2"/>
+      <c r="J102" s="2"/>
+      <c r="K102" s="2"/>
+      <c r="L102" s="2"/>
+      <c r="O102" s="1"/>
+      <c r="P102" s="2"/>
+      <c r="Q102" s="2"/>
+      <c r="R102" s="2"/>
+      <c r="S102" s="2"/>
+    </row>
+    <row r="103" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A103" s="1">
         <v>55900000</v>
       </c>
       <c r="B103" s="2">
-        <v>1372.03</v>
+        <v>2831.34</v>
       </c>
       <c r="C103" s="2">
-        <v>-87.727999999999994</v>
+        <v>-80.909000000000006</v>
       </c>
       <c r="D103" s="2">
-        <v>54.386400000000002</v>
+        <v>447.35599999999999</v>
       </c>
       <c r="E103" s="2">
-        <v>-1370.95</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-2795.77</v>
+      </c>
+      <c r="H103" s="1"/>
+      <c r="I103" s="2"/>
+      <c r="J103" s="2"/>
+      <c r="K103" s="2"/>
+      <c r="L103" s="2"/>
+      <c r="O103" s="1"/>
+      <c r="P103" s="2"/>
+      <c r="Q103" s="2"/>
+      <c r="R103" s="2"/>
+      <c r="S103" s="2"/>
+    </row>
+    <row r="104" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A104" s="1">
         <v>58200000</v>
       </c>
       <c r="B104" s="2">
-        <v>1320.91</v>
+        <v>2731.28</v>
       </c>
       <c r="C104" s="2">
-        <v>-87.447999999999993</v>
+        <v>-80.495000000000005</v>
       </c>
       <c r="D104" s="2">
-        <v>58.8157</v>
+        <v>451.04300000000001</v>
       </c>
       <c r="E104" s="2">
-        <v>-1319.6</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-2693.78</v>
+      </c>
+      <c r="H104" s="1"/>
+      <c r="I104" s="2"/>
+      <c r="J104" s="2"/>
+      <c r="K104" s="2"/>
+      <c r="L104" s="2"/>
+      <c r="O104" s="1"/>
+      <c r="P104" s="2"/>
+      <c r="Q104" s="2"/>
+      <c r="R104" s="2"/>
+      <c r="S104" s="2"/>
+    </row>
+    <row r="105" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A105" s="1">
         <v>60600000</v>
       </c>
       <c r="B105" s="2">
-        <v>1274.54</v>
+        <v>2646.51</v>
       </c>
       <c r="C105" s="2">
-        <v>-87.052000000000007</v>
+        <v>-79.826999999999998</v>
       </c>
       <c r="D105" s="2">
-        <v>65.545599999999993</v>
+        <v>467.41800000000001</v>
       </c>
       <c r="E105" s="2">
-        <v>-1272.8599999999999</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-2604.9</v>
+      </c>
+      <c r="H105" s="1"/>
+      <c r="I105" s="2"/>
+      <c r="J105" s="2"/>
+      <c r="K105" s="2"/>
+      <c r="L105" s="2"/>
+      <c r="O105" s="1"/>
+      <c r="P105" s="2"/>
+      <c r="Q105" s="2"/>
+      <c r="R105" s="2"/>
+      <c r="S105" s="2"/>
+    </row>
+    <row r="106" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A106" s="1">
         <v>63100000</v>
       </c>
       <c r="B106" s="2">
-        <v>1228.46</v>
+        <v>2556.42</v>
       </c>
       <c r="C106" s="2">
-        <v>-86.721999999999994</v>
+        <v>-79.31</v>
       </c>
       <c r="D106" s="2">
-        <v>70.245400000000004</v>
+        <v>474.18700000000001</v>
       </c>
       <c r="E106" s="2">
-        <v>-1226.45</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-2512.06</v>
+      </c>
+      <c r="H106" s="1"/>
+      <c r="I106" s="2"/>
+      <c r="J106" s="2"/>
+      <c r="K106" s="2"/>
+      <c r="L106" s="2"/>
+      <c r="O106" s="1"/>
+      <c r="P106" s="2"/>
+      <c r="Q106" s="2"/>
+      <c r="R106" s="2"/>
+      <c r="S106" s="2"/>
+    </row>
+    <row r="107" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A107" s="1">
         <v>65599999.999999993</v>
       </c>
       <c r="B107" s="2">
-        <v>1179.79</v>
+        <v>2456.89</v>
       </c>
       <c r="C107" s="2">
-        <v>-86.768000000000001</v>
+        <v>-79.552999999999997</v>
       </c>
       <c r="D107" s="2">
-        <v>66.521699999999996</v>
+        <v>445.49900000000002</v>
       </c>
       <c r="E107" s="2">
-        <v>-1177.9100000000001</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-2416.16</v>
+      </c>
+      <c r="H107" s="1"/>
+      <c r="I107" s="2"/>
+      <c r="J107" s="2"/>
+      <c r="K107" s="2"/>
+      <c r="L107" s="2"/>
+      <c r="O107" s="1"/>
+      <c r="P107" s="2"/>
+      <c r="Q107" s="2"/>
+      <c r="R107" s="2"/>
+      <c r="S107" s="2"/>
+    </row>
+    <row r="108" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A108" s="1">
         <v>68300000</v>
       </c>
       <c r="B108" s="2">
-        <v>1132.98</v>
+        <v>2355.4699999999998</v>
       </c>
       <c r="C108" s="2">
-        <v>-86.718999999999994</v>
+        <v>-79.605999999999995</v>
       </c>
       <c r="D108" s="2">
-        <v>64.845500000000001</v>
+        <v>424.964</v>
       </c>
       <c r="E108" s="2">
-        <v>-1131.1199999999999</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-2316.81</v>
+      </c>
+      <c r="H108" s="1"/>
+      <c r="I108" s="2"/>
+      <c r="J108" s="2"/>
+      <c r="K108" s="2"/>
+      <c r="L108" s="2"/>
+      <c r="O108" s="1"/>
+      <c r="P108" s="2"/>
+      <c r="Q108" s="2"/>
+      <c r="R108" s="2"/>
+      <c r="S108" s="2"/>
+    </row>
+    <row r="109" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A109" s="1">
         <v>71100000</v>
       </c>
       <c r="B109" s="2">
-        <v>1089.56</v>
+        <v>2268.62</v>
       </c>
       <c r="C109" s="2">
-        <v>-86.543999999999997</v>
+        <v>-79.361999999999995</v>
       </c>
       <c r="D109" s="2">
-        <v>65.682199999999995</v>
+        <v>418.80500000000001</v>
       </c>
       <c r="E109" s="2">
-        <v>-1087.58</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-2229.63</v>
+      </c>
+      <c r="H109" s="1"/>
+      <c r="I109" s="2"/>
+      <c r="J109" s="2"/>
+      <c r="K109" s="2"/>
+      <c r="L109" s="2"/>
+      <c r="O109" s="1"/>
+      <c r="P109" s="2"/>
+      <c r="Q109" s="2"/>
+      <c r="R109" s="2"/>
+      <c r="S109" s="2"/>
+    </row>
+    <row r="110" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A110" s="1">
         <v>74100000</v>
       </c>
       <c r="B110" s="2">
-        <v>1047.29</v>
+        <v>2179.25</v>
       </c>
       <c r="C110" s="2">
-        <v>-86.180999999999997</v>
+        <v>-78.799000000000007</v>
       </c>
       <c r="D110" s="2">
-        <v>69.750500000000002</v>
+        <v>423.31</v>
       </c>
       <c r="E110" s="2">
-        <v>-1044.96</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-2137.7399999999998</v>
+      </c>
+      <c r="H110" s="1"/>
+      <c r="I110" s="2"/>
+      <c r="J110" s="2"/>
+      <c r="K110" s="2"/>
+      <c r="L110" s="2"/>
+      <c r="O110" s="1"/>
+      <c r="P110" s="2"/>
+      <c r="Q110" s="2"/>
+      <c r="R110" s="2"/>
+      <c r="S110" s="2"/>
+    </row>
+    <row r="111" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A111" s="1">
         <v>77100000</v>
       </c>
       <c r="B111" s="2">
-        <v>1006.04</v>
+        <v>2092.4299999999998</v>
       </c>
       <c r="C111" s="2">
-        <v>-86.131</v>
+        <v>-78.825000000000003</v>
       </c>
       <c r="D111" s="2">
-        <v>67.883399999999995</v>
+        <v>405.53399999999999</v>
       </c>
       <c r="E111" s="2">
-        <v>-1003.75</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-2052.7600000000002</v>
+      </c>
+      <c r="H111" s="1"/>
+      <c r="I111" s="2"/>
+      <c r="J111" s="2"/>
+      <c r="K111" s="2"/>
+      <c r="L111" s="2"/>
+      <c r="O111" s="1"/>
+      <c r="P111" s="2"/>
+      <c r="Q111" s="2"/>
+      <c r="R111" s="2"/>
+      <c r="S111" s="2"/>
+    </row>
+    <row r="112" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A112" s="1">
         <v>80300000</v>
       </c>
       <c r="B112" s="2">
-        <v>965.75300000000004</v>
+        <v>2002.69</v>
       </c>
       <c r="C112" s="2">
-        <v>-86.105000000000004</v>
+        <v>-78.72</v>
       </c>
       <c r="D112" s="2">
-        <v>65.609200000000001</v>
+        <v>391.71800000000002</v>
       </c>
       <c r="E112" s="2">
-        <v>-963.52200000000005</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-1964.01</v>
+      </c>
+      <c r="H112" s="1"/>
+      <c r="I112" s="2"/>
+      <c r="J112" s="2"/>
+      <c r="K112" s="2"/>
+      <c r="L112" s="2"/>
+      <c r="O112" s="1"/>
+      <c r="P112" s="2"/>
+      <c r="Q112" s="2"/>
+      <c r="R112" s="2"/>
+      <c r="S112" s="2"/>
+    </row>
+    <row r="113" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A113" s="1">
         <v>83600000</v>
       </c>
       <c r="B113" s="2">
-        <v>927.95500000000004</v>
+        <v>1940.82</v>
       </c>
       <c r="C113" s="2">
-        <v>-85.900999999999996</v>
+        <v>-78.525999999999996</v>
       </c>
       <c r="D113" s="2">
-        <v>66.330600000000004</v>
+        <v>386.08300000000003</v>
       </c>
       <c r="E113" s="2">
-        <v>-925.58199999999999</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-1902.04</v>
+      </c>
+      <c r="H113" s="1"/>
+      <c r="I113" s="2"/>
+      <c r="J113" s="2"/>
+      <c r="K113" s="2"/>
+      <c r="L113" s="2"/>
+      <c r="O113" s="1"/>
+      <c r="P113" s="2"/>
+      <c r="Q113" s="2"/>
+      <c r="R113" s="2"/>
+      <c r="S113" s="2"/>
+    </row>
+    <row r="114" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A114" s="1">
         <v>87000000</v>
       </c>
       <c r="B114" s="2">
-        <v>893.3</v>
+        <v>1866.4</v>
       </c>
       <c r="C114" s="2">
-        <v>-85.471000000000004</v>
+        <v>-77.765000000000001</v>
       </c>
       <c r="D114" s="2">
-        <v>70.544200000000004</v>
+        <v>395.53800000000001</v>
       </c>
       <c r="E114" s="2">
-        <v>-890.51</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-1824.01</v>
+      </c>
+      <c r="H114" s="1"/>
+      <c r="I114" s="2"/>
+      <c r="J114" s="2"/>
+      <c r="K114" s="2"/>
+      <c r="L114" s="2"/>
+      <c r="O114" s="1"/>
+      <c r="P114" s="2"/>
+      <c r="Q114" s="2"/>
+      <c r="R114" s="2"/>
+      <c r="S114" s="2"/>
+    </row>
+    <row r="115" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A115" s="1">
         <v>90600000</v>
       </c>
       <c r="B115" s="2">
-        <v>856.68799999999999</v>
+        <v>1785.73</v>
       </c>
       <c r="C115" s="2">
-        <v>-85.474999999999994</v>
+        <v>-78.03</v>
       </c>
       <c r="D115" s="2">
-        <v>67.584800000000001</v>
+        <v>370.35700000000003</v>
       </c>
       <c r="E115" s="2">
-        <v>-854.01800000000003</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-1746.91</v>
+      </c>
+      <c r="H115" s="1"/>
+      <c r="I115" s="2"/>
+      <c r="J115" s="2"/>
+      <c r="K115" s="2"/>
+      <c r="L115" s="2"/>
+      <c r="O115" s="1"/>
+      <c r="P115" s="2"/>
+      <c r="Q115" s="2"/>
+      <c r="R115" s="2"/>
+      <c r="S115" s="2"/>
+    </row>
+    <row r="116" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A116" s="1">
         <v>94300000</v>
       </c>
       <c r="B116" s="2">
-        <v>822.96699999999998</v>
+        <v>1715.37</v>
       </c>
       <c r="C116" s="2">
-        <v>-85.364999999999995</v>
+        <v>-77.911000000000001</v>
       </c>
       <c r="D116" s="2">
-        <v>66.505300000000005</v>
+        <v>359.24400000000003</v>
       </c>
       <c r="E116" s="2">
-        <v>-820.27599999999995</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-1677.33</v>
+      </c>
+      <c r="H116" s="1"/>
+      <c r="I116" s="2"/>
+      <c r="J116" s="2"/>
+      <c r="K116" s="2"/>
+      <c r="L116" s="2"/>
+      <c r="O116" s="1"/>
+      <c r="P116" s="2"/>
+      <c r="Q116" s="2"/>
+      <c r="R116" s="2"/>
+      <c r="S116" s="2"/>
+    </row>
+    <row r="117" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A117" s="1">
         <v>98200000</v>
       </c>
       <c r="B117" s="2">
-        <v>791.78700000000003</v>
+        <v>1651.52</v>
       </c>
       <c r="C117" s="2">
-        <v>-84.998999999999995</v>
+        <v>-77.165999999999997</v>
       </c>
       <c r="D117" s="2">
-        <v>69.022300000000001</v>
+        <v>366.83699999999999</v>
       </c>
       <c r="E117" s="2">
-        <v>-788.77300000000002</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-1610.26</v>
+      </c>
+      <c r="H117" s="1"/>
+      <c r="I117" s="2"/>
+      <c r="J117" s="2"/>
+      <c r="K117" s="2"/>
+      <c r="L117" s="2"/>
+      <c r="O117" s="1"/>
+      <c r="P117" s="2"/>
+      <c r="Q117" s="2"/>
+      <c r="R117" s="2"/>
+      <c r="S117" s="2"/>
+    </row>
+    <row r="118" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A118" s="1">
         <v>102200000</v>
       </c>
       <c r="B118" s="2">
-        <v>760.63199999999995</v>
+        <v>1585.21</v>
       </c>
       <c r="C118" s="2">
-        <v>-84.8</v>
+        <v>-76.887</v>
       </c>
       <c r="D118" s="2">
-        <v>68.937899999999999</v>
+        <v>359.63299999999998</v>
       </c>
       <c r="E118" s="2">
-        <v>-757.50099999999998</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-1543.87</v>
+      </c>
+      <c r="H118" s="1"/>
+      <c r="I118" s="2"/>
+      <c r="J118" s="2"/>
+      <c r="K118" s="2"/>
+      <c r="L118" s="2"/>
+      <c r="O118" s="1"/>
+      <c r="P118" s="2"/>
+      <c r="Q118" s="2"/>
+      <c r="R118" s="2"/>
+      <c r="S118" s="2"/>
+    </row>
+    <row r="119" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A119" s="1">
         <v>106400000</v>
       </c>
       <c r="B119" s="2">
-        <v>730.04399999999998</v>
+        <v>1520.73</v>
       </c>
       <c r="C119" s="2">
-        <v>-84.69</v>
+        <v>-76.796999999999997</v>
       </c>
       <c r="D119" s="2">
-        <v>67.565200000000004</v>
+        <v>347.33699999999999</v>
       </c>
       <c r="E119" s="2">
-        <v>-726.91099999999994</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-1480.54</v>
+      </c>
+      <c r="H119" s="1"/>
+      <c r="I119" s="2"/>
+      <c r="J119" s="2"/>
+      <c r="K119" s="2"/>
+      <c r="L119" s="2"/>
+      <c r="O119" s="1"/>
+      <c r="P119" s="2"/>
+      <c r="Q119" s="2"/>
+      <c r="R119" s="2"/>
+      <c r="S119" s="2"/>
+    </row>
+    <row r="120" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A120" s="1">
         <v>110700000</v>
       </c>
       <c r="B120" s="2">
-        <v>703.26</v>
+        <v>1466.71</v>
       </c>
       <c r="C120" s="2">
-        <v>-84.353999999999999</v>
+        <v>-76.201999999999998</v>
       </c>
       <c r="D120" s="2">
-        <v>69.1905</v>
+        <v>349.79700000000003</v>
       </c>
       <c r="E120" s="2">
-        <v>-699.84799999999996</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-1424.39</v>
+      </c>
+      <c r="H120" s="1"/>
+      <c r="I120" s="2"/>
+      <c r="J120" s="2"/>
+      <c r="K120" s="2"/>
+      <c r="L120" s="2"/>
+      <c r="O120" s="1"/>
+      <c r="P120" s="2"/>
+      <c r="Q120" s="2"/>
+      <c r="R120" s="2"/>
+      <c r="S120" s="2"/>
+    </row>
+    <row r="121" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A121" s="1">
         <v>115300000</v>
       </c>
       <c r="B121" s="2">
-        <v>675.08299999999997</v>
+        <v>1407.96</v>
       </c>
       <c r="C121" s="2">
-        <v>-84.122</v>
+        <v>-75.822000000000003</v>
       </c>
       <c r="D121" s="2">
-        <v>69.130700000000004</v>
+        <v>344.85199999999998</v>
       </c>
       <c r="E121" s="2">
-        <v>-671.53399999999999</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-1365.07</v>
+      </c>
+      <c r="H121" s="1"/>
+      <c r="I121" s="2"/>
+      <c r="J121" s="2"/>
+      <c r="K121" s="2"/>
+      <c r="L121" s="2"/>
+      <c r="O121" s="1"/>
+      <c r="P121" s="2"/>
+      <c r="Q121" s="2"/>
+      <c r="R121" s="2"/>
+      <c r="S121" s="2"/>
+    </row>
+    <row r="122" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A122" s="1">
         <v>120000000</v>
       </c>
       <c r="B122" s="2">
-        <v>648.64800000000002</v>
+        <v>1351.3</v>
       </c>
       <c r="C122" s="2">
-        <v>-83.932000000000002</v>
+        <v>-75.540999999999997</v>
       </c>
       <c r="D122" s="2">
-        <v>68.563800000000001</v>
+        <v>337.39600000000002</v>
       </c>
       <c r="E122" s="2">
-        <v>-645.01400000000001</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-1308.5</v>
+      </c>
+      <c r="H122" s="1"/>
+      <c r="I122" s="2"/>
+      <c r="J122" s="2"/>
+      <c r="K122" s="2"/>
+      <c r="L122" s="2"/>
+      <c r="O122" s="1"/>
+      <c r="P122" s="2"/>
+      <c r="Q122" s="2"/>
+      <c r="R122" s="2"/>
+      <c r="S122" s="2"/>
+    </row>
+    <row r="123" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A123" s="1">
         <v>125000000</v>
       </c>
       <c r="B123" s="2">
-        <v>624.64099999999996</v>
+        <v>1303.07</v>
       </c>
       <c r="C123" s="2">
-        <v>-83.504000000000005</v>
+        <v>-74.685000000000002</v>
       </c>
       <c r="D123" s="2">
-        <v>70.666499999999999</v>
+        <v>344.17200000000003</v>
       </c>
       <c r="E123" s="2">
-        <v>-620.63099999999997</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-1256.79</v>
+      </c>
+      <c r="H123" s="1"/>
+      <c r="I123" s="2"/>
+      <c r="J123" s="2"/>
+      <c r="K123" s="2"/>
+      <c r="L123" s="2"/>
+      <c r="O123" s="1"/>
+      <c r="P123" s="2"/>
+      <c r="Q123" s="2"/>
+      <c r="R123" s="2"/>
+      <c r="S123" s="2"/>
+    </row>
+    <row r="124" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A124" s="1">
         <v>130100000</v>
       </c>
       <c r="B124" s="2">
-        <v>599.29600000000005</v>
+        <v>1249.6199999999999</v>
       </c>
       <c r="C124" s="2">
-        <v>-83.370999999999995</v>
+        <v>-74.576999999999998</v>
       </c>
       <c r="D124" s="2">
-        <v>69.186599999999999</v>
+        <v>332.31900000000002</v>
       </c>
       <c r="E124" s="2">
-        <v>-595.28899999999999</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-1204.6300000000001</v>
+      </c>
+      <c r="H124" s="1"/>
+      <c r="I124" s="2"/>
+      <c r="J124" s="2"/>
+      <c r="K124" s="2"/>
+      <c r="L124" s="2"/>
+      <c r="O124" s="1"/>
+      <c r="P124" s="2"/>
+      <c r="Q124" s="2"/>
+      <c r="R124" s="2"/>
+      <c r="S124" s="2"/>
+    </row>
+    <row r="125" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A125" s="1">
         <v>135400000</v>
       </c>
       <c r="B125" s="2">
-        <v>576.83600000000001</v>
+        <v>1202.79</v>
       </c>
       <c r="C125" s="2">
-        <v>-83.054000000000002</v>
+        <v>-74.001999999999995</v>
       </c>
       <c r="D125" s="2">
-        <v>69.762900000000002</v>
+        <v>331.49599999999998</v>
       </c>
       <c r="E125" s="2">
-        <v>-572.60199999999998</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-1156.21</v>
+      </c>
+      <c r="H125" s="1"/>
+      <c r="I125" s="2"/>
+      <c r="J125" s="2"/>
+      <c r="K125" s="2"/>
+      <c r="L125" s="2"/>
+      <c r="O125" s="1"/>
+      <c r="P125" s="2"/>
+      <c r="Q125" s="2"/>
+      <c r="R125" s="2"/>
+      <c r="S125" s="2"/>
+    </row>
+    <row r="126" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A126" s="1">
         <v>141000000</v>
       </c>
       <c r="B126" s="2">
-        <v>554.279</v>
+        <v>1155.43</v>
       </c>
       <c r="C126" s="2">
-        <v>-82.793000000000006</v>
+        <v>-73.503</v>
       </c>
       <c r="D126" s="2">
-        <v>69.540999999999997</v>
+        <v>328.09699999999998</v>
       </c>
       <c r="E126" s="2">
-        <v>-549.9</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-1107.8699999999999</v>
+      </c>
+      <c r="H126" s="1"/>
+      <c r="I126" s="2"/>
+      <c r="J126" s="2"/>
+      <c r="K126" s="2"/>
+      <c r="L126" s="2"/>
+      <c r="O126" s="1"/>
+      <c r="P126" s="2"/>
+      <c r="Q126" s="2"/>
+      <c r="R126" s="2"/>
+      <c r="S126" s="2"/>
+    </row>
+    <row r="127" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A127" s="1">
         <v>146800000</v>
       </c>
       <c r="B127" s="2">
-        <v>532.96699999999998</v>
+        <v>1110.43</v>
       </c>
       <c r="C127" s="2">
-        <v>-82.480999999999995</v>
+        <v>-72.992999999999995</v>
       </c>
       <c r="D127" s="2">
-        <v>69.738900000000001</v>
+        <v>324.78399999999999</v>
       </c>
       <c r="E127" s="2">
-        <v>-528.38400000000001</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-1061.8699999999999</v>
+      </c>
+      <c r="H127" s="1"/>
+      <c r="I127" s="2"/>
+      <c r="J127" s="2"/>
+      <c r="K127" s="2"/>
+      <c r="L127" s="2"/>
+      <c r="O127" s="1"/>
+      <c r="P127" s="2"/>
+      <c r="Q127" s="2"/>
+      <c r="R127" s="2"/>
+      <c r="S127" s="2"/>
+    </row>
+    <row r="128" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A128" s="1">
         <v>152800000</v>
       </c>
       <c r="B128" s="2">
-        <v>512.58199999999999</v>
+        <v>1068.2</v>
       </c>
       <c r="C128" s="2">
-        <v>-82.153000000000006</v>
+        <v>-72.414000000000001</v>
       </c>
       <c r="D128" s="2">
-        <v>69.977900000000005</v>
+        <v>322.74299999999999</v>
       </c>
       <c r="E128" s="2">
-        <v>-507.78300000000002</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-1018.28</v>
+      </c>
+      <c r="H128" s="1"/>
+      <c r="I128" s="2"/>
+      <c r="J128" s="2"/>
+      <c r="K128" s="2"/>
+      <c r="L128" s="2"/>
+      <c r="O128" s="1"/>
+      <c r="P128" s="2"/>
+      <c r="Q128" s="2"/>
+      <c r="R128" s="2"/>
+      <c r="S128" s="2"/>
+    </row>
+    <row r="129" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A129" s="1">
         <v>159100000</v>
       </c>
       <c r="B129" s="2">
-        <v>492.803</v>
+        <v>1026.6400000000001</v>
       </c>
       <c r="C129" s="2">
-        <v>-81.855000000000004</v>
+        <v>-71.873000000000005</v>
       </c>
       <c r="D129" s="2">
-        <v>69.819500000000005</v>
+        <v>319.41399999999999</v>
       </c>
       <c r="E129" s="2">
-        <v>-487.83199999999999</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-975.68299999999999</v>
+      </c>
+      <c r="H129" s="1"/>
+      <c r="I129" s="2"/>
+      <c r="J129" s="2"/>
+      <c r="K129" s="2"/>
+      <c r="L129" s="2"/>
+      <c r="O129" s="1"/>
+      <c r="P129" s="2"/>
+      <c r="Q129" s="2"/>
+      <c r="R129" s="2"/>
+      <c r="S129" s="2"/>
+    </row>
+    <row r="130" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A130" s="1">
         <v>165600000</v>
       </c>
       <c r="B130" s="2">
-        <v>473.95400000000001</v>
+        <v>986.09400000000005</v>
       </c>
       <c r="C130" s="2">
-        <v>-81.524000000000001</v>
+        <v>-71.227000000000004</v>
       </c>
       <c r="D130" s="2">
-        <v>69.855400000000003</v>
+        <v>317.33999999999997</v>
       </c>
       <c r="E130" s="2">
-        <v>-468.77800000000002</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-933.63599999999997</v>
+      </c>
+      <c r="H130" s="1"/>
+      <c r="I130" s="2"/>
+      <c r="J130" s="2"/>
+      <c r="K130" s="2"/>
+      <c r="L130" s="2"/>
+      <c r="O130" s="1"/>
+      <c r="P130" s="2"/>
+      <c r="Q130" s="2"/>
+      <c r="R130" s="2"/>
+      <c r="S130" s="2"/>
+    </row>
+    <row r="131" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A131" s="1">
         <v>172400000</v>
       </c>
       <c r="B131" s="2">
-        <v>455.916</v>
+        <v>949.96199999999999</v>
       </c>
       <c r="C131" s="2">
-        <v>-81.179000000000002</v>
+        <v>-70.616</v>
       </c>
       <c r="D131" s="2">
-        <v>69.912199999999999</v>
+        <v>315.28699999999998</v>
       </c>
       <c r="E131" s="2">
-        <v>-450.524</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-896.11500000000001</v>
+      </c>
+      <c r="H131" s="1"/>
+      <c r="I131" s="2"/>
+      <c r="J131" s="2"/>
+      <c r="K131" s="2"/>
+      <c r="L131" s="2"/>
+      <c r="O131" s="1"/>
+      <c r="P131" s="2"/>
+      <c r="Q131" s="2"/>
+      <c r="R131" s="2"/>
+      <c r="S131" s="2"/>
+    </row>
+    <row r="132" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A132" s="1">
         <v>179500000</v>
       </c>
       <c r="B132" s="2">
-        <v>438.13900000000001</v>
+        <v>912.14700000000005</v>
       </c>
       <c r="C132" s="2">
-        <v>-80.834000000000003</v>
+        <v>-69.941000000000003</v>
       </c>
       <c r="D132" s="2">
-        <v>69.794200000000004</v>
+        <v>312.85199999999998</v>
       </c>
       <c r="E132" s="2">
-        <v>-432.54399999999998</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-856.81700000000001</v>
+      </c>
+      <c r="H132" s="1"/>
+      <c r="I132" s="2"/>
+      <c r="J132" s="2"/>
+      <c r="K132" s="2"/>
+      <c r="L132" s="2"/>
+      <c r="O132" s="1"/>
+      <c r="P132" s="2"/>
+      <c r="Q132" s="2"/>
+      <c r="R132" s="2"/>
+      <c r="S132" s="2"/>
+    </row>
+    <row r="133" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A133" s="1">
         <v>186800000</v>
       </c>
       <c r="B133" s="2">
-        <v>422.19900000000001</v>
+        <v>877.98599999999999</v>
       </c>
       <c r="C133" s="2">
-        <v>-80.397000000000006</v>
+        <v>-69.253</v>
       </c>
       <c r="D133" s="2">
-        <v>70.433300000000003</v>
+        <v>311.02499999999998</v>
       </c>
       <c r="E133" s="2">
-        <v>-416.28300000000002</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-821.05</v>
+      </c>
+      <c r="H133" s="1"/>
+      <c r="I133" s="2"/>
+      <c r="J133" s="2"/>
+      <c r="K133" s="2"/>
+      <c r="L133" s="2"/>
+      <c r="O133" s="1"/>
+      <c r="P133" s="2"/>
+      <c r="Q133" s="2"/>
+      <c r="R133" s="2"/>
+      <c r="S133" s="2"/>
+    </row>
+    <row r="134" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A134" s="1">
         <v>194500000</v>
       </c>
       <c r="B134" s="2">
-        <v>405.58499999999998</v>
+        <v>842.745</v>
       </c>
       <c r="C134" s="2">
-        <v>-80.039000000000001</v>
+        <v>-68.497</v>
       </c>
       <c r="D134" s="2">
-        <v>70.159000000000006</v>
+        <v>308.90600000000001</v>
       </c>
       <c r="E134" s="2">
-        <v>-399.471</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-784.08900000000006</v>
+      </c>
+      <c r="H134" s="1"/>
+      <c r="I134" s="2"/>
+      <c r="J134" s="2"/>
+      <c r="K134" s="2"/>
+      <c r="L134" s="2"/>
+      <c r="O134" s="1"/>
+      <c r="P134" s="2"/>
+      <c r="Q134" s="2"/>
+      <c r="R134" s="2"/>
+      <c r="S134" s="2"/>
+    </row>
+    <row r="135" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A135" s="1">
         <v>202500000</v>
       </c>
       <c r="B135" s="2">
-        <v>390.58100000000002</v>
+        <v>812.91600000000005</v>
       </c>
       <c r="C135" s="2">
-        <v>-79.613</v>
+        <v>-67.602999999999994</v>
       </c>
       <c r="D135" s="2">
-        <v>70.42</v>
+        <v>309.738</v>
       </c>
       <c r="E135" s="2">
-        <v>-384.18</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-751.59500000000003</v>
+      </c>
+      <c r="H135" s="1"/>
+      <c r="I135" s="2"/>
+      <c r="J135" s="2"/>
+      <c r="K135" s="2"/>
+      <c r="L135" s="2"/>
+      <c r="O135" s="1"/>
+      <c r="P135" s="2"/>
+      <c r="Q135" s="2"/>
+      <c r="R135" s="2"/>
+      <c r="S135" s="2"/>
+    </row>
+    <row r="136" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A136" s="1">
         <v>210800000</v>
       </c>
       <c r="B136" s="2">
-        <v>376.03899999999999</v>
+        <v>782.56200000000001</v>
       </c>
       <c r="C136" s="2">
-        <v>-79.191000000000003</v>
+        <v>-66.83</v>
       </c>
       <c r="D136" s="2">
-        <v>70.520700000000005</v>
+        <v>307.91000000000003</v>
       </c>
       <c r="E136" s="2">
-        <v>-369.36799999999999</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-719.44</v>
+      </c>
+      <c r="H136" s="1"/>
+      <c r="I136" s="2"/>
+      <c r="J136" s="2"/>
+      <c r="K136" s="2"/>
+      <c r="L136" s="2"/>
+      <c r="O136" s="1"/>
+      <c r="P136" s="2"/>
+      <c r="Q136" s="2"/>
+      <c r="R136" s="2"/>
+      <c r="S136" s="2"/>
+    </row>
+    <row r="137" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A137" s="1">
         <v>219500000</v>
       </c>
       <c r="B137" s="2">
-        <v>361.72899999999998</v>
+        <v>752.798</v>
       </c>
       <c r="C137" s="2">
-        <v>-78.801000000000002</v>
+        <v>-66.103999999999999</v>
       </c>
       <c r="D137" s="2">
-        <v>70.251499999999993</v>
+        <v>304.93599999999998</v>
       </c>
       <c r="E137" s="2">
-        <v>-354.84100000000001</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-688.27300000000002</v>
+      </c>
+      <c r="H137" s="1"/>
+      <c r="I137" s="2"/>
+      <c r="J137" s="2"/>
+      <c r="K137" s="2"/>
+      <c r="L137" s="2"/>
+      <c r="O137" s="1"/>
+      <c r="P137" s="2"/>
+      <c r="Q137" s="2"/>
+      <c r="R137" s="2"/>
+      <c r="S137" s="2"/>
+    </row>
+    <row r="138" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A138" s="1">
         <v>228500000</v>
       </c>
       <c r="B138" s="2">
-        <v>348.30399999999997</v>
+        <v>724.90700000000004</v>
       </c>
       <c r="C138" s="2">
-        <v>-78.349999999999994</v>
+        <v>-65.234999999999999</v>
       </c>
       <c r="D138" s="2">
-        <v>70.333500000000001</v>
+        <v>303.65800000000002</v>
       </c>
       <c r="E138" s="2">
-        <v>-341.12900000000002</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-658.24199999999996</v>
+      </c>
+      <c r="H138" s="1"/>
+      <c r="I138" s="2"/>
+      <c r="J138" s="2"/>
+      <c r="K138" s="2"/>
+      <c r="L138" s="2"/>
+      <c r="O138" s="1"/>
+      <c r="P138" s="2"/>
+      <c r="Q138" s="2"/>
+      <c r="R138" s="2"/>
+      <c r="S138" s="2"/>
+    </row>
+    <row r="139" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A139" s="1">
         <v>237900000</v>
       </c>
       <c r="B139" s="2">
-        <v>335.49799999999999</v>
+        <v>698.21900000000005</v>
       </c>
       <c r="C139" s="2">
-        <v>-77.846000000000004</v>
+        <v>-64.204999999999998</v>
       </c>
       <c r="D139" s="2">
-        <v>70.636600000000001</v>
+        <v>303.83499999999998</v>
       </c>
       <c r="E139" s="2">
-        <v>-327.97800000000001</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-628.64400000000001</v>
+      </c>
+      <c r="H139" s="1"/>
+      <c r="I139" s="2"/>
+      <c r="J139" s="2"/>
+      <c r="K139" s="2"/>
+      <c r="L139" s="2"/>
+      <c r="O139" s="1"/>
+      <c r="P139" s="2"/>
+      <c r="Q139" s="2"/>
+      <c r="R139" s="2"/>
+      <c r="S139" s="2"/>
+    </row>
+    <row r="140" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A140" s="1">
         <v>247600000</v>
       </c>
       <c r="B140" s="2">
-        <v>323.01900000000001</v>
+        <v>671.91800000000001</v>
       </c>
       <c r="C140" s="2">
-        <v>-77.403000000000006</v>
+        <v>-63.363</v>
       </c>
       <c r="D140" s="2">
-        <v>70.450699999999998</v>
+        <v>301.24200000000002</v>
       </c>
       <c r="E140" s="2">
-        <v>-315.24299999999999</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-600.60500000000002</v>
+      </c>
+      <c r="H140" s="1"/>
+      <c r="I140" s="2"/>
+      <c r="J140" s="2"/>
+      <c r="K140" s="2"/>
+      <c r="L140" s="2"/>
+      <c r="O140" s="1"/>
+      <c r="P140" s="2"/>
+      <c r="Q140" s="2"/>
+      <c r="R140" s="2"/>
+      <c r="S140" s="2"/>
+    </row>
+    <row r="141" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A141" s="1">
         <v>257800000</v>
       </c>
       <c r="B141" s="2">
-        <v>310.98399999999998</v>
+        <v>647.01499999999999</v>
       </c>
       <c r="C141" s="2">
-        <v>-76.899000000000001</v>
+        <v>-62.408999999999999</v>
       </c>
       <c r="D141" s="2">
-        <v>70.489099999999993</v>
+        <v>299.67200000000003</v>
       </c>
       <c r="E141" s="2">
-        <v>-302.89</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-573.43299999999999</v>
+      </c>
+      <c r="H141" s="1"/>
+      <c r="I141" s="2"/>
+      <c r="J141" s="2"/>
+      <c r="K141" s="2"/>
+      <c r="L141" s="2"/>
+      <c r="O141" s="1"/>
+      <c r="P141" s="2"/>
+      <c r="Q141" s="2"/>
+      <c r="R141" s="2"/>
+      <c r="S141" s="2"/>
+    </row>
+    <row r="142" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A142" s="1">
         <v>268399999.99999997</v>
       </c>
       <c r="B142" s="2">
-        <v>299.68099999999998</v>
+        <v>623.75300000000004</v>
       </c>
       <c r="C142" s="2">
-        <v>-76.394999999999996</v>
+        <v>-61.427999999999997</v>
       </c>
       <c r="D142" s="2">
-        <v>70.493899999999996</v>
+        <v>298.32100000000003</v>
       </c>
       <c r="E142" s="2">
-        <v>-291.27199999999999</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-547.78899999999999</v>
+      </c>
+      <c r="H142" s="1"/>
+      <c r="I142" s="2"/>
+      <c r="J142" s="2"/>
+      <c r="K142" s="2"/>
+      <c r="L142" s="2"/>
+      <c r="O142" s="1"/>
+      <c r="P142" s="2"/>
+      <c r="Q142" s="2"/>
+      <c r="R142" s="2"/>
+      <c r="S142" s="2"/>
+    </row>
+    <row r="143" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A143" s="1">
         <v>279400000</v>
       </c>
       <c r="B143" s="2">
-        <v>288.87299999999999</v>
+        <v>601.47299999999996</v>
       </c>
       <c r="C143" s="2">
-        <v>-75.873999999999995</v>
+        <v>-60.375999999999998</v>
       </c>
       <c r="D143" s="2">
-        <v>70.502700000000004</v>
+        <v>297.315</v>
       </c>
       <c r="E143" s="2">
-        <v>-280.137</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-522.85199999999998</v>
+      </c>
+      <c r="H143" s="1"/>
+      <c r="I143" s="2"/>
+      <c r="J143" s="2"/>
+      <c r="K143" s="2"/>
+      <c r="L143" s="2"/>
+      <c r="O143" s="1"/>
+      <c r="P143" s="2"/>
+      <c r="Q143" s="2"/>
+      <c r="R143" s="2"/>
+      <c r="S143" s="2"/>
+    </row>
+    <row r="144" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A144" s="1">
         <v>290900000</v>
       </c>
       <c r="B144" s="2">
-        <v>278.411</v>
+        <v>578.86400000000003</v>
       </c>
       <c r="C144" s="2">
-        <v>-75.334000000000003</v>
+        <v>-59.308999999999997</v>
       </c>
       <c r="D144" s="2">
-        <v>70.487499999999997</v>
+        <v>295.45699999999999</v>
       </c>
       <c r="E144" s="2">
-        <v>-269.34100000000001</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-497.78399999999999</v>
+      </c>
+      <c r="H144" s="1"/>
+      <c r="I144" s="2"/>
+      <c r="J144" s="2"/>
+      <c r="K144" s="2"/>
+      <c r="L144" s="2"/>
+      <c r="O144" s="1"/>
+      <c r="P144" s="2"/>
+      <c r="Q144" s="2"/>
+      <c r="R144" s="2"/>
+      <c r="S144" s="2"/>
+    </row>
+    <row r="145" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A145" s="1">
         <v>302800000</v>
       </c>
       <c r="B145" s="2">
-        <v>268.44</v>
+        <v>557.851</v>
       </c>
       <c r="C145" s="2">
-        <v>-74.766000000000005</v>
+        <v>-58.156999999999996</v>
       </c>
       <c r="D145" s="2">
-        <v>70.535799999999995</v>
+        <v>294.31900000000002</v>
       </c>
       <c r="E145" s="2">
-        <v>-259.00799999999998</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-473.89299999999997</v>
+      </c>
+      <c r="H145" s="1"/>
+      <c r="I145" s="2"/>
+      <c r="J145" s="2"/>
+      <c r="K145" s="2"/>
+      <c r="L145" s="2"/>
+      <c r="O145" s="1"/>
+      <c r="P145" s="2"/>
+      <c r="Q145" s="2"/>
+      <c r="R145" s="2"/>
+      <c r="S145" s="2"/>
+    </row>
+    <row r="146" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A146" s="1">
         <v>315200000</v>
       </c>
       <c r="B146" s="2">
-        <v>258.91500000000002</v>
+        <v>537.83699999999999</v>
       </c>
       <c r="C146" s="2">
-        <v>-74.174999999999997</v>
+        <v>-56.981999999999999</v>
       </c>
       <c r="D146" s="2">
-        <v>70.607500000000002</v>
+        <v>293.06900000000002</v>
       </c>
       <c r="E146" s="2">
-        <v>-249.101</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-450.976</v>
+      </c>
+      <c r="H146" s="1"/>
+      <c r="I146" s="2"/>
+      <c r="J146" s="2"/>
+      <c r="K146" s="2"/>
+      <c r="L146" s="2"/>
+      <c r="O146" s="1"/>
+      <c r="P146" s="2"/>
+      <c r="Q146" s="2"/>
+      <c r="R146" s="2"/>
+      <c r="S146" s="2"/>
+    </row>
+    <row r="147" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A147" s="1">
         <v>328200000</v>
       </c>
       <c r="B147" s="2">
-        <v>249.77600000000001</v>
+        <v>519.15599999999995</v>
       </c>
       <c r="C147" s="2">
-        <v>-73.569999999999993</v>
+        <v>-55.728999999999999</v>
       </c>
       <c r="D147" s="2">
-        <v>70.649199999999993</v>
+        <v>292.34399999999999</v>
       </c>
       <c r="E147" s="2">
-        <v>-239.57599999999999</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-429.02</v>
+      </c>
+      <c r="H147" s="1"/>
+      <c r="I147" s="2"/>
+      <c r="J147" s="2"/>
+      <c r="K147" s="2"/>
+      <c r="L147" s="2"/>
+      <c r="O147" s="1"/>
+      <c r="P147" s="2"/>
+      <c r="Q147" s="2"/>
+      <c r="R147" s="2"/>
+      <c r="S147" s="2"/>
+    </row>
+    <row r="148" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A148" s="1">
         <v>341600000</v>
       </c>
       <c r="B148" s="2">
-        <v>241.11699999999999</v>
+        <v>500.73</v>
       </c>
       <c r="C148" s="2">
-        <v>-72.97</v>
+        <v>-54.561999999999998</v>
       </c>
       <c r="D148" s="2">
-        <v>70.614699999999999</v>
+        <v>290.33199999999999</v>
       </c>
       <c r="E148" s="2">
-        <v>-230.54400000000001</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-407.96800000000002</v>
+      </c>
+      <c r="H148" s="1"/>
+      <c r="I148" s="2"/>
+      <c r="J148" s="2"/>
+      <c r="K148" s="2"/>
+      <c r="L148" s="2"/>
+      <c r="O148" s="1"/>
+      <c r="P148" s="2"/>
+      <c r="Q148" s="2"/>
+      <c r="R148" s="2"/>
+      <c r="S148" s="2"/>
+    </row>
+    <row r="149" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A149" s="1">
         <v>355700000</v>
       </c>
       <c r="B149" s="2">
-        <v>232.69499999999999</v>
+        <v>482.93400000000003</v>
       </c>
       <c r="C149" s="2">
-        <v>-72.349000000000004</v>
+        <v>-53.250999999999998</v>
       </c>
       <c r="D149" s="2">
-        <v>70.559200000000004</v>
+        <v>288.94099999999997</v>
       </c>
       <c r="E149" s="2">
-        <v>-221.74</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-386.96</v>
+      </c>
+      <c r="H149" s="1"/>
+      <c r="I149" s="2"/>
+      <c r="J149" s="2"/>
+      <c r="K149" s="2"/>
+      <c r="L149" s="2"/>
+      <c r="O149" s="1"/>
+      <c r="P149" s="2"/>
+      <c r="Q149" s="2"/>
+      <c r="R149" s="2"/>
+      <c r="S149" s="2"/>
+    </row>
+    <row r="150" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A150" s="1">
         <v>370300000</v>
       </c>
       <c r="B150" s="2">
-        <v>224.69499999999999</v>
+        <v>466.12200000000001</v>
       </c>
       <c r="C150" s="2">
-        <v>-71.685000000000002</v>
+        <v>-51.887</v>
       </c>
       <c r="D150" s="2">
-        <v>70.607100000000003</v>
+        <v>287.69600000000003</v>
       </c>
       <c r="E150" s="2">
-        <v>-213.31299999999999</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-366.74400000000003</v>
+      </c>
+      <c r="H150" s="1"/>
+      <c r="I150" s="2"/>
+      <c r="J150" s="2"/>
+      <c r="K150" s="2"/>
+      <c r="L150" s="2"/>
+      <c r="O150" s="1"/>
+      <c r="P150" s="2"/>
+      <c r="Q150" s="2"/>
+      <c r="R150" s="2"/>
+      <c r="S150" s="2"/>
+    </row>
+    <row r="151" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A151" s="1">
         <v>385500000</v>
       </c>
       <c r="B151" s="2">
-        <v>217.114</v>
+        <v>450.45699999999999</v>
       </c>
       <c r="C151" s="2">
-        <v>-71.001999999999995</v>
+        <v>-50.521000000000001</v>
       </c>
       <c r="D151" s="2">
-        <v>70.676599999999993</v>
+        <v>286.399</v>
       </c>
       <c r="E151" s="2">
-        <v>-205.28899999999999</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-347.68700000000001</v>
+      </c>
+      <c r="H151" s="1"/>
+      <c r="I151" s="2"/>
+      <c r="J151" s="2"/>
+      <c r="K151" s="2"/>
+      <c r="L151" s="2"/>
+      <c r="O151" s="1"/>
+      <c r="P151" s="2"/>
+      <c r="Q151" s="2"/>
+      <c r="R151" s="2"/>
+      <c r="S151" s="2"/>
+    </row>
+    <row r="152" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A152" s="1">
         <v>401300000</v>
       </c>
       <c r="B152" s="2">
-        <v>209.916</v>
+        <v>434.92700000000002</v>
       </c>
       <c r="C152" s="2">
-        <v>-70.320999999999998</v>
+        <v>-49.136000000000003</v>
       </c>
       <c r="D152" s="2">
-        <v>70.689300000000003</v>
+        <v>284.55599999999998</v>
       </c>
       <c r="E152" s="2">
-        <v>-197.65600000000001</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-328.92099999999999</v>
+      </c>
+      <c r="H152" s="1"/>
+      <c r="I152" s="2"/>
+      <c r="J152" s="2"/>
+      <c r="K152" s="2"/>
+      <c r="L152" s="2"/>
+      <c r="O152" s="1"/>
+      <c r="P152" s="2"/>
+      <c r="Q152" s="2"/>
+      <c r="R152" s="2"/>
+      <c r="S152" s="2"/>
+    </row>
+    <row r="153" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A153" s="1">
         <v>417800000</v>
       </c>
       <c r="B153" s="2">
-        <v>202.91300000000001</v>
+        <v>419.72800000000001</v>
       </c>
       <c r="C153" s="2">
-        <v>-69.644999999999996</v>
+        <v>-47.658000000000001</v>
       </c>
       <c r="D153" s="2">
-        <v>70.578800000000001</v>
+        <v>282.71199999999999</v>
       </c>
       <c r="E153" s="2">
-        <v>-190.24299999999999</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-310.23399999999998</v>
+      </c>
+      <c r="H153" s="1"/>
+      <c r="I153" s="2"/>
+      <c r="J153" s="2"/>
+      <c r="K153" s="2"/>
+      <c r="L153" s="2"/>
+      <c r="O153" s="1"/>
+      <c r="P153" s="2"/>
+      <c r="Q153" s="2"/>
+      <c r="R153" s="2"/>
+      <c r="S153" s="2"/>
+    </row>
+    <row r="154" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A154" s="1">
         <v>434900000</v>
       </c>
       <c r="B154" s="2">
-        <v>196.25899999999999</v>
+        <v>405.68</v>
       </c>
       <c r="C154" s="2">
-        <v>-68.927999999999997</v>
+        <v>-46.137</v>
       </c>
       <c r="D154" s="2">
-        <v>70.561700000000002</v>
+        <v>281.11200000000002</v>
       </c>
       <c r="E154" s="2">
-        <v>-183.136</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-292.49299999999999</v>
+      </c>
+      <c r="H154" s="1"/>
+      <c r="I154" s="2"/>
+      <c r="J154" s="2"/>
+      <c r="K154" s="2"/>
+      <c r="L154" s="2"/>
+      <c r="O154" s="1"/>
+      <c r="P154" s="2"/>
+      <c r="Q154" s="2"/>
+      <c r="R154" s="2"/>
+      <c r="S154" s="2"/>
+    </row>
+    <row r="155" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A155" s="1">
         <v>452800000</v>
       </c>
       <c r="B155" s="2">
-        <v>189.93199999999999</v>
+        <v>391.99799999999999</v>
       </c>
       <c r="C155" s="2">
-        <v>-68.191999999999993</v>
+        <v>-44.581000000000003</v>
       </c>
       <c r="D155" s="2">
-        <v>70.557900000000004</v>
+        <v>279.20299999999997</v>
       </c>
       <c r="E155" s="2">
-        <v>-176.34</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-275.15199999999999</v>
+      </c>
+      <c r="H155" s="1"/>
+      <c r="I155" s="2"/>
+      <c r="J155" s="2"/>
+      <c r="K155" s="2"/>
+      <c r="L155" s="2"/>
+      <c r="O155" s="1"/>
+      <c r="P155" s="2"/>
+      <c r="Q155" s="2"/>
+      <c r="R155" s="2"/>
+      <c r="S155" s="2"/>
+    </row>
+    <row r="156" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A156" s="1">
         <v>471400000</v>
       </c>
       <c r="B156" s="2">
-        <v>183.876</v>
+        <v>378.81400000000002</v>
       </c>
       <c r="C156" s="2">
-        <v>-67.463999999999999</v>
+        <v>-43.021999999999998</v>
       </c>
       <c r="D156" s="2">
-        <v>70.473100000000002</v>
+        <v>276.94900000000001</v>
       </c>
       <c r="E156" s="2">
-        <v>-169.83500000000001</v>
-      </c>
-    </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-258.45499999999998</v>
+      </c>
+      <c r="H156" s="1"/>
+      <c r="I156" s="2"/>
+      <c r="J156" s="2"/>
+      <c r="K156" s="2"/>
+      <c r="L156" s="2"/>
+      <c r="O156" s="1"/>
+      <c r="P156" s="2"/>
+      <c r="Q156" s="2"/>
+      <c r="R156" s="2"/>
+      <c r="S156" s="2"/>
+    </row>
+    <row r="157" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A157" s="1">
         <v>490700000</v>
       </c>
       <c r="B157" s="2">
-        <v>178.065</v>
+        <v>366.12</v>
       </c>
       <c r="C157" s="2">
-        <v>-66.712999999999994</v>
+        <v>-41.417999999999999</v>
       </c>
       <c r="D157" s="2">
-        <v>70.394499999999994</v>
+        <v>274.55599999999998</v>
       </c>
       <c r="E157" s="2">
-        <v>-163.56</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-242.20400000000001</v>
+      </c>
+      <c r="H157" s="1"/>
+      <c r="I157" s="2"/>
+      <c r="J157" s="2"/>
+      <c r="K157" s="2"/>
+      <c r="L157" s="2"/>
+      <c r="O157" s="1"/>
+      <c r="P157" s="2"/>
+      <c r="Q157" s="2"/>
+      <c r="R157" s="2"/>
+      <c r="S157" s="2"/>
+    </row>
+    <row r="158" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A158" s="1">
         <v>510900000</v>
       </c>
       <c r="B158" s="2">
-        <v>172.56899999999999</v>
+        <v>353.96100000000001</v>
       </c>
       <c r="C158" s="2">
-        <v>-65.927000000000007</v>
+        <v>-39.701999999999998</v>
       </c>
       <c r="D158" s="2">
-        <v>70.391300000000001</v>
+        <v>272.33100000000002</v>
       </c>
       <c r="E158" s="2">
-        <v>-157.559</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-226.107</v>
+      </c>
+      <c r="H158" s="1"/>
+      <c r="I158" s="2"/>
+      <c r="J158" s="2"/>
+      <c r="K158" s="2"/>
+      <c r="L158" s="2"/>
+      <c r="O158" s="1"/>
+      <c r="P158" s="2"/>
+      <c r="Q158" s="2"/>
+      <c r="R158" s="2"/>
+      <c r="S158" s="2"/>
+    </row>
+    <row r="159" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A159" s="1">
         <v>531799999.99999994</v>
       </c>
       <c r="B159" s="2">
-        <v>167.39500000000001</v>
+        <v>342.61599999999999</v>
       </c>
       <c r="C159" s="2">
-        <v>-65.138000000000005</v>
+        <v>-37.954000000000001</v>
       </c>
       <c r="D159" s="2">
-        <v>70.377899999999997</v>
+        <v>270.154</v>
       </c>
       <c r="E159" s="2">
-        <v>-151.88200000000001</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-210.71799999999999</v>
+      </c>
+      <c r="H159" s="1"/>
+      <c r="I159" s="2"/>
+      <c r="J159" s="2"/>
+      <c r="K159" s="2"/>
+      <c r="L159" s="2"/>
+      <c r="O159" s="1"/>
+      <c r="P159" s="2"/>
+      <c r="Q159" s="2"/>
+      <c r="R159" s="2"/>
+      <c r="S159" s="2"/>
+    </row>
+    <row r="160" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A160" s="1">
         <v>553700000</v>
       </c>
       <c r="B160" s="2">
-        <v>162.38200000000001</v>
+        <v>331.38299999999998</v>
       </c>
       <c r="C160" s="2">
-        <v>-64.337999999999994</v>
+        <v>-36.194000000000003</v>
       </c>
       <c r="D160" s="2">
-        <v>70.321799999999996</v>
+        <v>267.435</v>
       </c>
       <c r="E160" s="2">
-        <v>-146.36500000000001</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-195.68700000000001</v>
+      </c>
+      <c r="H160" s="1"/>
+      <c r="I160" s="2"/>
+      <c r="J160" s="2"/>
+      <c r="K160" s="2"/>
+      <c r="L160" s="2"/>
+      <c r="O160" s="1"/>
+      <c r="P160" s="2"/>
+      <c r="Q160" s="2"/>
+      <c r="R160" s="2"/>
+      <c r="S160" s="2"/>
+    </row>
+    <row r="161" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A161" s="1">
         <v>576400000</v>
       </c>
       <c r="B161" s="2">
-        <v>157.69300000000001</v>
+        <v>320.92200000000003</v>
       </c>
       <c r="C161" s="2">
-        <v>-63.518999999999998</v>
+        <v>-34.357999999999997</v>
       </c>
       <c r="D161" s="2">
-        <v>70.315200000000004</v>
+        <v>264.92899999999997</v>
       </c>
       <c r="E161" s="2">
-        <v>-141.148</v>
-      </c>
-    </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-181.11799999999999</v>
+      </c>
+      <c r="H161" s="1"/>
+      <c r="I161" s="2"/>
+      <c r="J161" s="2"/>
+      <c r="K161" s="2"/>
+      <c r="L161" s="2"/>
+      <c r="O161" s="1"/>
+      <c r="P161" s="2"/>
+      <c r="Q161" s="2"/>
+      <c r="R161" s="2"/>
+      <c r="S161" s="2"/>
+    </row>
+    <row r="162" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A162" s="1">
         <v>600100000</v>
       </c>
       <c r="B162" s="2">
-        <v>153.19900000000001</v>
+        <v>310.678</v>
       </c>
       <c r="C162" s="2">
-        <v>-62.695999999999998</v>
+        <v>-32.523000000000003</v>
       </c>
       <c r="D162" s="2">
-        <v>70.274299999999997</v>
+        <v>261.95699999999999</v>
       </c>
       <c r="E162" s="2">
-        <v>-136.13</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-167.03</v>
+      </c>
+      <c r="H162" s="1"/>
+      <c r="I162" s="2"/>
+      <c r="J162" s="2"/>
+      <c r="K162" s="2"/>
+      <c r="L162" s="2"/>
+      <c r="O162" s="1"/>
+      <c r="P162" s="2"/>
+      <c r="Q162" s="2"/>
+      <c r="R162" s="2"/>
+      <c r="S162" s="2"/>
+    </row>
+    <row r="163" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A163" s="1">
         <v>624700000</v>
       </c>
       <c r="B163" s="2">
-        <v>148.94300000000001</v>
+        <v>300.85500000000002</v>
       </c>
       <c r="C163" s="2">
-        <v>-61.878999999999998</v>
+        <v>-30.634</v>
       </c>
       <c r="D163" s="2">
-        <v>70.202600000000004</v>
+        <v>258.86900000000003</v>
       </c>
       <c r="E163" s="2">
-        <v>-131.36099999999999</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-153.30000000000001</v>
+      </c>
+      <c r="H163" s="1"/>
+      <c r="I163" s="2"/>
+      <c r="J163" s="2"/>
+      <c r="K163" s="2"/>
+      <c r="L163" s="2"/>
+      <c r="O163" s="1"/>
+      <c r="P163" s="2"/>
+      <c r="Q163" s="2"/>
+      <c r="R163" s="2"/>
+      <c r="S163" s="2"/>
+    </row>
+    <row r="164" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A164" s="1">
         <v>650400000</v>
       </c>
       <c r="B164" s="2">
-        <v>144.827</v>
+        <v>291.75700000000001</v>
       </c>
       <c r="C164" s="2">
-        <v>-61.057000000000002</v>
+        <v>-28.713999999999999</v>
       </c>
       <c r="D164" s="2">
-        <v>70.086600000000004</v>
+        <v>255.88</v>
       </c>
       <c r="E164" s="2">
-        <v>-126.738</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-140.16999999999999</v>
+      </c>
+      <c r="H164" s="1"/>
+      <c r="I164" s="2"/>
+      <c r="J164" s="2"/>
+      <c r="K164" s="2"/>
+      <c r="L164" s="2"/>
+      <c r="O164" s="1"/>
+      <c r="P164" s="2"/>
+      <c r="Q164" s="2"/>
+      <c r="R164" s="2"/>
+      <c r="S164" s="2"/>
+    </row>
+    <row r="165" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A165" s="1">
         <v>677100000</v>
       </c>
       <c r="B165" s="2">
-        <v>140.93600000000001</v>
+        <v>282.70999999999998</v>
       </c>
       <c r="C165" s="2">
-        <v>-60.228999999999999</v>
+        <v>-26.818999999999999</v>
       </c>
       <c r="D165" s="2">
-        <v>69.979299999999995</v>
+        <v>252.30099999999999</v>
       </c>
       <c r="E165" s="2">
-        <v>-122.33499999999999</v>
-      </c>
-    </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-127.55</v>
+      </c>
+      <c r="H165" s="1"/>
+      <c r="I165" s="2"/>
+      <c r="J165" s="2"/>
+      <c r="K165" s="2"/>
+      <c r="L165" s="2"/>
+      <c r="O165" s="1"/>
+      <c r="P165" s="2"/>
+      <c r="Q165" s="2"/>
+      <c r="R165" s="2"/>
+      <c r="S165" s="2"/>
+    </row>
+    <row r="166" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A166" s="1">
         <v>704800000</v>
       </c>
       <c r="B166" s="2">
-        <v>137.238</v>
+        <v>274.06599999999997</v>
       </c>
       <c r="C166" s="2">
-        <v>-59.377000000000002</v>
+        <v>-24.829000000000001</v>
       </c>
       <c r="D166" s="2">
-        <v>69.906099999999995</v>
+        <v>248.732</v>
       </c>
       <c r="E166" s="2">
-        <v>-118.099</v>
-      </c>
-    </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-115.08499999999999</v>
+      </c>
+      <c r="H166" s="1"/>
+      <c r="I166" s="2"/>
+      <c r="J166" s="2"/>
+      <c r="K166" s="2"/>
+      <c r="L166" s="2"/>
+      <c r="O166" s="1"/>
+      <c r="P166" s="2"/>
+      <c r="Q166" s="2"/>
+      <c r="R166" s="2"/>
+      <c r="S166" s="2"/>
+    </row>
+    <row r="167" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A167" s="1">
         <v>733800000</v>
       </c>
       <c r="B167" s="2">
-        <v>133.75399999999999</v>
+        <v>265.92200000000003</v>
       </c>
       <c r="C167" s="2">
-        <v>-58.533999999999999</v>
+        <v>-22.826000000000001</v>
       </c>
       <c r="D167" s="2">
-        <v>69.817999999999998</v>
+        <v>245.096</v>
       </c>
       <c r="E167" s="2">
-        <v>-114.08499999999999</v>
-      </c>
-    </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-103.161</v>
+      </c>
+      <c r="H167" s="1"/>
+      <c r="I167" s="2"/>
+      <c r="J167" s="2"/>
+      <c r="K167" s="2"/>
+      <c r="L167" s="2"/>
+      <c r="O167" s="1"/>
+      <c r="P167" s="2"/>
+      <c r="Q167" s="2"/>
+      <c r="R167" s="2"/>
+      <c r="S167" s="2"/>
+    </row>
+    <row r="168" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A168" s="1">
         <v>763900000</v>
       </c>
       <c r="B168" s="2">
-        <v>130.51900000000001</v>
+        <v>258.03500000000003</v>
       </c>
       <c r="C168" s="2">
-        <v>-57.69</v>
+        <v>-20.774000000000001</v>
       </c>
       <c r="D168" s="2">
-        <v>69.762</v>
+        <v>241.26</v>
       </c>
       <c r="E168" s="2">
-        <v>-110.31100000000001</v>
-      </c>
-    </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-91.520099999999999</v>
+      </c>
+      <c r="H168" s="1"/>
+      <c r="I168" s="2"/>
+      <c r="J168" s="2"/>
+      <c r="K168" s="2"/>
+      <c r="L168" s="2"/>
+      <c r="O168" s="1"/>
+      <c r="P168" s="2"/>
+      <c r="Q168" s="2"/>
+      <c r="R168" s="2"/>
+      <c r="S168" s="2"/>
+    </row>
+    <row r="169" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A169" s="1">
         <v>795300000</v>
       </c>
       <c r="B169" s="2">
-        <v>127.38800000000001</v>
+        <v>250.619</v>
       </c>
       <c r="C169" s="2">
-        <v>-56.884</v>
+        <v>-18.779</v>
       </c>
       <c r="D169" s="2">
-        <v>69.597499999999997</v>
+        <v>237.27699999999999</v>
       </c>
       <c r="E169" s="2">
-        <v>-106.696</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-80.679900000000004</v>
+      </c>
+      <c r="H169" s="1"/>
+      <c r="I169" s="2"/>
+      <c r="J169" s="2"/>
+      <c r="K169" s="2"/>
+      <c r="L169" s="2"/>
+      <c r="O169" s="1"/>
+      <c r="P169" s="2"/>
+      <c r="Q169" s="2"/>
+      <c r="R169" s="2"/>
+      <c r="S169" s="2"/>
+    </row>
+    <row r="170" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A170" s="1">
         <v>827900000</v>
       </c>
       <c r="B170" s="2">
-        <v>124.402</v>
+        <v>243.05699999999999</v>
       </c>
       <c r="C170" s="2">
-        <v>-56.058</v>
+        <v>-16.602</v>
       </c>
       <c r="D170" s="2">
-        <v>69.459699999999998</v>
+        <v>232.92500000000001</v>
       </c>
       <c r="E170" s="2">
-        <v>-103.205</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-69.444999999999993</v>
+      </c>
+      <c r="H170" s="1"/>
+      <c r="I170" s="2"/>
+      <c r="J170" s="2"/>
+      <c r="K170" s="2"/>
+      <c r="L170" s="2"/>
+      <c r="O170" s="1"/>
+      <c r="P170" s="2"/>
+      <c r="Q170" s="2"/>
+      <c r="R170" s="2"/>
+      <c r="S170" s="2"/>
+    </row>
+    <row r="171" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A171" s="1">
         <v>861900000</v>
       </c>
       <c r="B171" s="2">
-        <v>121.602</v>
+        <v>236.173</v>
       </c>
       <c r="C171" s="2">
-        <v>-55.249000000000002</v>
+        <v>-14.455</v>
       </c>
       <c r="D171" s="2">
-        <v>69.313500000000005</v>
+        <v>228.697</v>
       </c>
       <c r="E171" s="2">
-        <v>-99.912999999999997</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-58.951900000000002</v>
+      </c>
+      <c r="H171" s="1"/>
+      <c r="I171" s="2"/>
+      <c r="J171" s="2"/>
+      <c r="K171" s="2"/>
+      <c r="L171" s="2"/>
+      <c r="O171" s="1"/>
+      <c r="P171" s="2"/>
+      <c r="Q171" s="2"/>
+      <c r="R171" s="2"/>
+      <c r="S171" s="2"/>
+    </row>
+    <row r="172" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A172" s="1">
         <v>897300000</v>
       </c>
       <c r="B172" s="2">
-        <v>118.92</v>
+        <v>230.065</v>
       </c>
       <c r="C172" s="2">
-        <v>-54.442</v>
+        <v>-12.41</v>
       </c>
       <c r="D172" s="2">
-        <v>69.155100000000004</v>
+        <v>224.68899999999999</v>
       </c>
       <c r="E172" s="2">
-        <v>-96.744799999999998</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-49.442</v>
+      </c>
+      <c r="H172" s="1"/>
+      <c r="I172" s="2"/>
+      <c r="J172" s="2"/>
+      <c r="K172" s="2"/>
+      <c r="L172" s="2"/>
+      <c r="O172" s="1"/>
+      <c r="P172" s="2"/>
+      <c r="Q172" s="2"/>
+      <c r="R172" s="2"/>
+      <c r="S172" s="2"/>
+    </row>
+    <row r="173" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A173" s="1">
         <v>934100000</v>
       </c>
       <c r="B173" s="2">
-        <v>116.39100000000001</v>
+        <v>222.428</v>
       </c>
       <c r="C173" s="2">
-        <v>-53.643999999999998</v>
+        <v>-10.167</v>
       </c>
       <c r="D173" s="2">
-        <v>68.996499999999997</v>
+        <v>218.93600000000001</v>
       </c>
       <c r="E173" s="2">
-        <v>-93.736099999999993</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-39.261400000000002</v>
+      </c>
+      <c r="H173" s="1"/>
+      <c r="I173" s="2"/>
+      <c r="J173" s="2"/>
+      <c r="K173" s="2"/>
+      <c r="L173" s="2"/>
+      <c r="O173" s="1"/>
+      <c r="P173" s="2"/>
+      <c r="Q173" s="2"/>
+      <c r="R173" s="2"/>
+      <c r="S173" s="2"/>
+    </row>
+    <row r="174" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A174" s="1">
         <v>972500000</v>
       </c>
       <c r="B174" s="2">
-        <v>114.006</v>
+        <v>216.23</v>
       </c>
       <c r="C174" s="2">
-        <v>-52.859000000000002</v>
+        <v>-7.9939999999999998</v>
       </c>
       <c r="D174" s="2">
-        <v>68.834800000000001</v>
+        <v>214.12799999999999</v>
       </c>
       <c r="E174" s="2">
-        <v>-90.879499999999993</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-30.0715</v>
+      </c>
+      <c r="H174" s="1"/>
+      <c r="I174" s="2"/>
+      <c r="J174" s="2"/>
+      <c r="K174" s="2"/>
+      <c r="L174" s="2"/>
+      <c r="O174" s="1"/>
+      <c r="P174" s="2"/>
+      <c r="Q174" s="2"/>
+      <c r="R174" s="2"/>
+      <c r="S174" s="2"/>
+    </row>
+    <row r="175" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A175" s="1">
         <v>1012400000</v>
       </c>
       <c r="B175" s="2">
-        <v>111.705</v>
+        <v>209.39500000000001</v>
       </c>
       <c r="C175" s="2">
-        <v>-52.106000000000002</v>
+        <v>-5.7539999999999996</v>
       </c>
       <c r="D175" s="2">
-        <v>68.610200000000006</v>
+        <v>208.34</v>
       </c>
       <c r="E175" s="2">
-        <v>-88.151700000000005</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-20.991700000000002</v>
+      </c>
+      <c r="H175" s="1"/>
+      <c r="I175" s="2"/>
+      <c r="J175" s="2"/>
+      <c r="K175" s="2"/>
+      <c r="L175" s="2"/>
+      <c r="O175" s="1"/>
+      <c r="P175" s="2"/>
+      <c r="Q175" s="2"/>
+      <c r="R175" s="2"/>
+      <c r="S175" s="2"/>
+    </row>
+    <row r="176" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A176" s="1">
         <v>1054000000</v>
       </c>
       <c r="B176" s="2">
-        <v>109.551</v>
+        <v>203.226</v>
       </c>
       <c r="C176" s="2">
-        <v>-51.360999999999997</v>
+        <v>-3.5880000000000001</v>
       </c>
       <c r="D176" s="2">
-        <v>68.405100000000004</v>
+        <v>202.828</v>
       </c>
       <c r="E176" s="2">
-        <v>-85.57</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-12.718999999999999</v>
+      </c>
+      <c r="H176" s="1"/>
+      <c r="I176" s="2"/>
+      <c r="J176" s="2"/>
+      <c r="K176" s="2"/>
+      <c r="L176" s="2"/>
+      <c r="O176" s="1"/>
+      <c r="P176" s="2"/>
+      <c r="Q176" s="2"/>
+      <c r="R176" s="2"/>
+      <c r="S176" s="2"/>
+    </row>
+    <row r="177" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A177" s="1">
         <v>1097200000</v>
       </c>
       <c r="B177" s="2">
-        <v>107.47799999999999</v>
+        <v>196.86699999999999</v>
       </c>
       <c r="C177" s="2">
-        <v>-50.646999999999998</v>
+        <v>-1.4039999999999999</v>
       </c>
       <c r="D177" s="2">
-        <v>68.1511</v>
+        <v>196.80799999999999</v>
       </c>
       <c r="E177" s="2">
-        <v>-83.107699999999994</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-4.8237100000000002</v>
+      </c>
+      <c r="H177" s="1"/>
+      <c r="I177" s="2"/>
+      <c r="J177" s="2"/>
+      <c r="K177" s="2"/>
+      <c r="L177" s="2"/>
+      <c r="O177" s="1"/>
+      <c r="P177" s="2"/>
+      <c r="Q177" s="2"/>
+      <c r="R177" s="2"/>
+      <c r="S177" s="2"/>
+    </row>
+    <row r="178" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A178" s="1">
         <v>1142300000</v>
       </c>
       <c r="B178" s="2">
-        <v>105.511</v>
+        <v>191.00899999999999</v>
       </c>
       <c r="C178" s="2">
-        <v>-49.95</v>
+        <v>0.81100000000000005</v>
       </c>
       <c r="D178" s="2">
-        <v>67.892600000000002</v>
+        <v>190.99</v>
       </c>
       <c r="E178" s="2">
-        <v>-80.766800000000003</v>
-      </c>
-    </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2.7031000000000001</v>
+      </c>
+      <c r="H178" s="1"/>
+      <c r="I178" s="2"/>
+      <c r="J178" s="2"/>
+      <c r="K178" s="2"/>
+      <c r="L178" s="2"/>
+      <c r="O178" s="1"/>
+      <c r="P178" s="2"/>
+      <c r="Q178" s="2"/>
+      <c r="R178" s="2"/>
+      <c r="S178" s="2"/>
+    </row>
+    <row r="179" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A179" s="1">
         <v>1189200000</v>
       </c>
       <c r="B179" s="2">
-        <v>103.66</v>
+        <v>185.15299999999999</v>
       </c>
       <c r="C179" s="2">
-        <v>-49.287999999999997</v>
+        <v>2.8780000000000001</v>
       </c>
       <c r="D179" s="2">
-        <v>67.612399999999994</v>
+        <v>184.92</v>
       </c>
       <c r="E179" s="2">
-        <v>-78.574700000000007</v>
-      </c>
-    </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+        <v>9.2951800000000002</v>
+      </c>
+      <c r="H179" s="1"/>
+      <c r="I179" s="2"/>
+      <c r="J179" s="2"/>
+      <c r="K179" s="2"/>
+      <c r="L179" s="2"/>
+      <c r="O179" s="1"/>
+      <c r="P179" s="2"/>
+      <c r="Q179" s="2"/>
+      <c r="R179" s="2"/>
+      <c r="S179" s="2"/>
+    </row>
+    <row r="180" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A180" s="1">
         <v>1238000000</v>
       </c>
       <c r="B180" s="2">
-        <v>101.869</v>
+        <v>179.68299999999999</v>
       </c>
       <c r="C180" s="2">
-        <v>-48.642000000000003</v>
+        <v>5.1230000000000002</v>
       </c>
       <c r="D180" s="2">
-        <v>67.310900000000004</v>
+        <v>178.965</v>
       </c>
       <c r="E180" s="2">
-        <v>-76.463200000000001</v>
-      </c>
-    </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+        <v>16.043700000000001</v>
+      </c>
+      <c r="H180" s="1"/>
+      <c r="I180" s="2"/>
+      <c r="J180" s="2"/>
+      <c r="K180" s="2"/>
+      <c r="L180" s="2"/>
+      <c r="O180" s="1"/>
+      <c r="P180" s="2"/>
+      <c r="Q180" s="2"/>
+      <c r="R180" s="2"/>
+      <c r="S180" s="2"/>
+    </row>
+    <row r="181" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A181" s="1">
         <v>1288800000</v>
       </c>
       <c r="B181" s="2">
-        <v>100.196</v>
+        <v>174.29400000000001</v>
       </c>
       <c r="C181" s="2">
-        <v>-48.04</v>
+        <v>7.1689999999999996</v>
       </c>
       <c r="D181" s="2">
-        <v>66.992800000000003</v>
+        <v>172.93100000000001</v>
       </c>
       <c r="E181" s="2">
-        <v>-74.506500000000003</v>
-      </c>
-    </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+        <v>21.7498</v>
+      </c>
+      <c r="H181" s="1"/>
+      <c r="I181" s="2"/>
+      <c r="J181" s="2"/>
+      <c r="K181" s="2"/>
+      <c r="L181" s="2"/>
+      <c r="O181" s="1"/>
+      <c r="P181" s="2"/>
+      <c r="Q181" s="2"/>
+      <c r="R181" s="2"/>
+      <c r="S181" s="2"/>
+    </row>
+    <row r="182" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A182" s="1">
         <v>1341700000</v>
       </c>
       <c r="B182" s="2">
-        <v>98.596000000000004</v>
+        <v>168.63800000000001</v>
       </c>
       <c r="C182" s="2">
-        <v>-47.45</v>
+        <v>9.36</v>
       </c>
       <c r="D182" s="2">
-        <v>66.674099999999996</v>
+        <v>166.393</v>
       </c>
       <c r="E182" s="2">
-        <v>-72.634200000000007</v>
-      </c>
-    </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+        <v>27.426500000000001</v>
+      </c>
+      <c r="H182" s="1"/>
+      <c r="I182" s="2"/>
+      <c r="J182" s="2"/>
+      <c r="K182" s="2"/>
+      <c r="L182" s="2"/>
+      <c r="O182" s="1"/>
+      <c r="P182" s="2"/>
+      <c r="Q182" s="2"/>
+      <c r="R182" s="2"/>
+      <c r="S182" s="2"/>
+    </row>
+    <row r="183" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A183" s="1">
         <v>1396800000</v>
       </c>
       <c r="B183" s="2">
-        <v>97.047499999999999</v>
+        <v>163.49600000000001</v>
       </c>
       <c r="C183" s="2">
-        <v>-46.933999999999997</v>
+        <v>11.539</v>
       </c>
       <c r="D183" s="2">
-        <v>66.268100000000004</v>
+        <v>160.191</v>
       </c>
       <c r="E183" s="2">
-        <v>-70.899600000000007</v>
-      </c>
-    </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+        <v>32.7042</v>
+      </c>
+      <c r="H183" s="1"/>
+      <c r="I183" s="2"/>
+      <c r="J183" s="2"/>
+      <c r="K183" s="2"/>
+      <c r="L183" s="2"/>
+      <c r="O183" s="1"/>
+      <c r="P183" s="2"/>
+      <c r="Q183" s="2"/>
+      <c r="R183" s="2"/>
+      <c r="S183" s="2"/>
+    </row>
+    <row r="184" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A184" s="1">
         <v>1454100000</v>
       </c>
       <c r="B184" s="2">
-        <v>95.543099999999995</v>
+        <v>158.13499999999999</v>
       </c>
       <c r="C184" s="2">
-        <v>-46.417999999999999</v>
+        <v>13.648999999999999</v>
       </c>
       <c r="D184" s="2">
-        <v>65.866799999999998</v>
+        <v>153.66900000000001</v>
       </c>
       <c r="E184" s="2">
-        <v>-69.2102</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+        <v>37.314399999999999</v>
+      </c>
+      <c r="H184" s="1"/>
+      <c r="I184" s="2"/>
+      <c r="J184" s="2"/>
+      <c r="K184" s="2"/>
+      <c r="L184" s="2"/>
+      <c r="O184" s="1"/>
+      <c r="P184" s="2"/>
+      <c r="Q184" s="2"/>
+      <c r="R184" s="2"/>
+      <c r="S184" s="2"/>
+    </row>
+    <row r="185" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A185" s="1">
         <v>1513800000</v>
       </c>
       <c r="B185" s="2">
-        <v>94.072900000000004</v>
+        <v>152.792</v>
       </c>
       <c r="C185" s="2">
-        <v>-45.96</v>
+        <v>15.817</v>
       </c>
       <c r="D185" s="2">
-        <v>65.396100000000004</v>
+        <v>147.006</v>
       </c>
       <c r="E185" s="2">
-        <v>-67.624499999999998</v>
-      </c>
-    </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+        <v>41.646000000000001</v>
+      </c>
+      <c r="H185" s="1"/>
+      <c r="I185" s="2"/>
+      <c r="J185" s="2"/>
+      <c r="K185" s="2"/>
+      <c r="L185" s="2"/>
+      <c r="O185" s="1"/>
+      <c r="P185" s="2"/>
+      <c r="Q185" s="2"/>
+      <c r="R185" s="2"/>
+      <c r="S185" s="2"/>
+    </row>
+    <row r="186" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A186" s="1">
         <v>1576000000</v>
       </c>
       <c r="B186" s="2">
-        <v>92.73</v>
+        <v>147.31700000000001</v>
       </c>
       <c r="C186" s="2">
-        <v>-45.523000000000003</v>
+        <v>17.899000000000001</v>
       </c>
       <c r="D186" s="2">
-        <v>64.968800000000002</v>
+        <v>140.18700000000001</v>
       </c>
       <c r="E186" s="2">
-        <v>-66.165800000000004</v>
-      </c>
-    </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+        <v>45.275799999999997</v>
+      </c>
+      <c r="H186" s="1"/>
+      <c r="I186" s="2"/>
+      <c r="J186" s="2"/>
+      <c r="K186" s="2"/>
+      <c r="L186" s="2"/>
+      <c r="O186" s="1"/>
+      <c r="P186" s="2"/>
+      <c r="Q186" s="2"/>
+      <c r="R186" s="2"/>
+      <c r="S186" s="2"/>
+    </row>
+    <row r="187" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A187" s="1">
         <v>1640700000</v>
       </c>
       <c r="B187" s="2">
-        <v>91.351399999999998</v>
+        <v>142.05000000000001</v>
       </c>
       <c r="C187" s="2">
-        <v>-45.139000000000003</v>
+        <v>19.791</v>
       </c>
       <c r="D187" s="2">
-        <v>64.438500000000005</v>
+        <v>133.66</v>
       </c>
       <c r="E187" s="2">
-        <v>-64.751400000000004</v>
-      </c>
-    </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+        <v>48.097799999999999</v>
+      </c>
+      <c r="H187" s="1"/>
+      <c r="I187" s="2"/>
+      <c r="J187" s="2"/>
+      <c r="K187" s="2"/>
+      <c r="L187" s="2"/>
+      <c r="O187" s="1"/>
+      <c r="P187" s="2"/>
+      <c r="Q187" s="2"/>
+      <c r="R187" s="2"/>
+      <c r="S187" s="2"/>
+    </row>
+    <row r="188" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A188" s="1">
         <v>1708000000</v>
       </c>
       <c r="B188" s="2">
-        <v>90.019800000000004</v>
+        <v>137.042</v>
       </c>
       <c r="C188" s="2">
-        <v>-44.829000000000001</v>
+        <v>21.616</v>
       </c>
       <c r="D188" s="2">
-        <v>63.843600000000002</v>
+        <v>127.405</v>
       </c>
       <c r="E188" s="2">
-        <v>-63.463000000000001</v>
-      </c>
-    </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+        <v>50.4846</v>
+      </c>
+      <c r="H188" s="1"/>
+      <c r="I188" s="2"/>
+      <c r="J188" s="2"/>
+      <c r="K188" s="2"/>
+      <c r="L188" s="2"/>
+      <c r="O188" s="1"/>
+      <c r="P188" s="2"/>
+      <c r="Q188" s="2"/>
+      <c r="R188" s="2"/>
+      <c r="S188" s="2"/>
+    </row>
+    <row r="189" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A189" s="1">
         <v>1778200000</v>
       </c>
       <c r="B189" s="2">
-        <v>88.759600000000006</v>
+        <v>132.14400000000001</v>
       </c>
       <c r="C189" s="2">
-        <v>-44.500999999999998</v>
+        <v>23.434999999999999</v>
       </c>
       <c r="D189" s="2">
-        <v>63.307000000000002</v>
+        <v>121.244</v>
       </c>
       <c r="E189" s="2">
-        <v>-62.213299999999997</v>
-      </c>
-    </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+        <v>52.555100000000003</v>
+      </c>
+      <c r="H189" s="1"/>
+      <c r="I189" s="2"/>
+      <c r="J189" s="2"/>
+      <c r="K189" s="2"/>
+      <c r="L189" s="2"/>
+      <c r="O189" s="1"/>
+      <c r="P189" s="2"/>
+      <c r="Q189" s="2"/>
+      <c r="R189" s="2"/>
+      <c r="S189" s="2"/>
+    </row>
+    <row r="190" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A190" s="1">
         <v>1851200000</v>
       </c>
       <c r="B190" s="2">
-        <v>87.586100000000002</v>
+        <v>127.49299999999999</v>
       </c>
       <c r="C190" s="2">
-        <v>-44.261000000000003</v>
+        <v>25.495999999999999</v>
       </c>
       <c r="D190" s="2">
-        <v>62.726300000000002</v>
+        <v>115.07599999999999</v>
       </c>
       <c r="E190" s="2">
-        <v>-61.128900000000002</v>
-      </c>
-    </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+        <v>54.879899999999999</v>
+      </c>
+      <c r="H190" s="1"/>
+      <c r="I190" s="2"/>
+      <c r="J190" s="2"/>
+      <c r="K190" s="2"/>
+      <c r="L190" s="2"/>
+      <c r="O190" s="1"/>
+      <c r="P190" s="2"/>
+      <c r="Q190" s="2"/>
+      <c r="R190" s="2"/>
+      <c r="S190" s="2"/>
+    </row>
+    <row r="191" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A191" s="1">
         <v>1927200000</v>
       </c>
       <c r="B191" s="2">
-        <v>86.344300000000004</v>
+        <v>122.925</v>
       </c>
       <c r="C191" s="2">
-        <v>-44.08</v>
+        <v>27.526</v>
       </c>
       <c r="D191" s="2">
-        <v>62.027099999999997</v>
+        <v>109.01</v>
       </c>
       <c r="E191" s="2">
-        <v>-60.066400000000002</v>
-      </c>
-    </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+        <v>56.810699999999997</v>
+      </c>
+      <c r="H191" s="1"/>
+      <c r="I191" s="2"/>
+      <c r="J191" s="2"/>
+      <c r="K191" s="2"/>
+      <c r="L191" s="2"/>
+      <c r="O191" s="1"/>
+      <c r="P191" s="2"/>
+      <c r="Q191" s="2"/>
+      <c r="R191" s="2"/>
+      <c r="S191" s="2"/>
+    </row>
+    <row r="192" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A192" s="1">
         <v>2006300000</v>
       </c>
       <c r="B192" s="2">
-        <v>85.201099999999997</v>
+        <v>118.181</v>
       </c>
       <c r="C192" s="2">
-        <v>-43.893000000000001</v>
+        <v>29.291</v>
       </c>
       <c r="D192" s="2">
-        <v>61.3994</v>
+        <v>103.071</v>
       </c>
       <c r="E192" s="2">
-        <v>-59.070700000000002</v>
-      </c>
-    </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+        <v>57.820300000000003</v>
+      </c>
+      <c r="H192" s="1"/>
+      <c r="I192" s="2"/>
+      <c r="J192" s="2"/>
+      <c r="K192" s="2"/>
+      <c r="L192" s="2"/>
+      <c r="O192" s="1"/>
+      <c r="P192" s="2"/>
+      <c r="Q192" s="2"/>
+      <c r="R192" s="2"/>
+      <c r="S192" s="2"/>
+    </row>
+    <row r="193" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A193" s="1">
         <v>2088600000</v>
       </c>
       <c r="B193" s="2">
-        <v>84.174099999999996</v>
+        <v>113.34</v>
       </c>
       <c r="C193" s="2">
-        <v>-43.805</v>
+        <v>31.073</v>
       </c>
       <c r="D193" s="2">
-        <v>60.748399999999997</v>
+        <v>97.076800000000006</v>
       </c>
       <c r="E193" s="2">
-        <v>-58.265799999999999</v>
-      </c>
-    </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+        <v>58.498600000000003</v>
+      </c>
+      <c r="H193" s="1"/>
+      <c r="I193" s="2"/>
+      <c r="J193" s="2"/>
+      <c r="K193" s="2"/>
+      <c r="L193" s="2"/>
+      <c r="O193" s="1"/>
+      <c r="P193" s="2"/>
+      <c r="Q193" s="2"/>
+      <c r="R193" s="2"/>
+      <c r="S193" s="2"/>
+    </row>
+    <row r="194" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A194" s="1">
         <v>2174400000</v>
       </c>
       <c r="B194" s="2">
-        <v>82.988699999999994</v>
+        <v>108.566</v>
       </c>
       <c r="C194" s="2">
-        <v>-43.738999999999997</v>
+        <v>32.655999999999999</v>
       </c>
       <c r="D194" s="2">
-        <v>59.958799999999997</v>
+        <v>91.403999999999996</v>
       </c>
       <c r="E194" s="2">
-        <v>-57.376600000000003</v>
-      </c>
-    </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+        <v>58.582299999999996</v>
+      </c>
+      <c r="H194" s="1"/>
+      <c r="I194" s="2"/>
+      <c r="J194" s="2"/>
+      <c r="K194" s="2"/>
+      <c r="L194" s="2"/>
+      <c r="O194" s="1"/>
+      <c r="P194" s="2"/>
+      <c r="Q194" s="2"/>
+      <c r="R194" s="2"/>
+      <c r="S194" s="2"/>
+    </row>
+    <row r="195" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A195" s="1">
         <v>2263700000</v>
       </c>
       <c r="B195" s="2">
-        <v>82.020200000000003</v>
+        <v>103.996</v>
       </c>
       <c r="C195" s="2">
-        <v>-43.723999999999997</v>
+        <v>34.122999999999998</v>
       </c>
       <c r="D195" s="2">
-        <v>59.273899999999998</v>
+        <v>86.091499999999996</v>
       </c>
       <c r="E195" s="2">
-        <v>-56.691400000000002</v>
-      </c>
-    </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+        <v>58.3386</v>
+      </c>
+      <c r="H195" s="1"/>
+      <c r="I195" s="2"/>
+      <c r="J195" s="2"/>
+      <c r="K195" s="2"/>
+      <c r="L195" s="2"/>
+      <c r="O195" s="1"/>
+      <c r="P195" s="2"/>
+      <c r="Q195" s="2"/>
+      <c r="R195" s="2"/>
+      <c r="S195" s="2"/>
+    </row>
+    <row r="196" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A196" s="1">
         <v>2356600000</v>
       </c>
       <c r="B196" s="2">
-        <v>80.921599999999998</v>
+        <v>99.628200000000007</v>
       </c>
       <c r="C196" s="2">
-        <v>-43.790999999999997</v>
+        <v>35.576000000000001</v>
       </c>
       <c r="D196" s="2">
-        <v>58.414700000000003</v>
+        <v>81.031899999999993</v>
       </c>
       <c r="E196" s="2">
-        <v>-56.0002</v>
-      </c>
-    </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+        <v>57.9621</v>
+      </c>
+      <c r="H196" s="1"/>
+      <c r="I196" s="2"/>
+      <c r="J196" s="2"/>
+      <c r="K196" s="2"/>
+      <c r="L196" s="2"/>
+      <c r="O196" s="1"/>
+      <c r="P196" s="2"/>
+      <c r="Q196" s="2"/>
+      <c r="R196" s="2"/>
+      <c r="S196" s="2"/>
+    </row>
+    <row r="197" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A197" s="1">
         <v>2453300000</v>
       </c>
       <c r="B197" s="2">
-        <v>79.881399999999999</v>
+        <v>95.465199999999996</v>
       </c>
       <c r="C197" s="2">
-        <v>-43.814999999999998</v>
+        <v>37.052</v>
       </c>
       <c r="D197" s="2">
-        <v>57.6404</v>
+        <v>76.189899999999994</v>
       </c>
       <c r="E197" s="2">
-        <v>-55.3048</v>
-      </c>
-    </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+        <v>57.5214</v>
+      </c>
+      <c r="H197" s="1"/>
+      <c r="I197" s="2"/>
+      <c r="J197" s="2"/>
+      <c r="K197" s="2"/>
+      <c r="L197" s="2"/>
+      <c r="O197" s="1"/>
+      <c r="P197" s="2"/>
+      <c r="Q197" s="2"/>
+      <c r="R197" s="2"/>
+      <c r="S197" s="2"/>
+    </row>
+    <row r="198" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A198" s="1">
         <v>2554000000</v>
       </c>
       <c r="B198" s="2">
-        <v>78.867099999999994</v>
+        <v>91.256100000000004</v>
       </c>
       <c r="C198" s="2">
-        <v>-43.936</v>
+        <v>38.439</v>
       </c>
       <c r="D198" s="2">
-        <v>56.792900000000003</v>
+        <v>71.478200000000001</v>
       </c>
       <c r="E198" s="2">
-        <v>-54.722700000000003</v>
-      </c>
-    </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+        <v>56.732300000000002</v>
+      </c>
+      <c r="H198" s="1"/>
+      <c r="I198" s="2"/>
+      <c r="J198" s="2"/>
+      <c r="K198" s="2"/>
+      <c r="L198" s="2"/>
+      <c r="O198" s="1"/>
+      <c r="P198" s="2"/>
+      <c r="Q198" s="2"/>
+      <c r="R198" s="2"/>
+      <c r="S198" s="2"/>
+    </row>
+    <row r="199" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A199" s="1">
         <v>2658900000</v>
       </c>
       <c r="B199" s="2">
-        <v>77.702200000000005</v>
+        <v>86.775400000000005</v>
       </c>
       <c r="C199" s="2">
-        <v>-44.03</v>
+        <v>39.835000000000001</v>
       </c>
       <c r="D199" s="2">
-        <v>55.8658</v>
+        <v>66.634399999999999</v>
       </c>
       <c r="E199" s="2">
-        <v>-54.005899999999997</v>
-      </c>
-    </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+        <v>55.586199999999998</v>
+      </c>
+      <c r="H199" s="1"/>
+      <c r="I199" s="2"/>
+      <c r="J199" s="2"/>
+      <c r="K199" s="2"/>
+      <c r="L199" s="2"/>
+      <c r="O199" s="1"/>
+      <c r="P199" s="2"/>
+      <c r="Q199" s="2"/>
+      <c r="R199" s="2"/>
+      <c r="S199" s="2"/>
+    </row>
+    <row r="200" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A200" s="1">
         <v>2768100000</v>
       </c>
       <c r="B200" s="2">
-        <v>76.576800000000006</v>
+        <v>81.979500000000002</v>
       </c>
       <c r="C200" s="2">
-        <v>-44.023000000000003</v>
+        <v>41.088999999999999</v>
       </c>
       <c r="D200" s="2">
-        <v>55.063499999999998</v>
+        <v>61.786799999999999</v>
       </c>
       <c r="E200" s="2">
-        <v>-53.216799999999999</v>
-      </c>
-    </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+        <v>53.8797</v>
+      </c>
+      <c r="H200" s="1"/>
+      <c r="I200" s="2"/>
+      <c r="J200" s="2"/>
+      <c r="K200" s="2"/>
+      <c r="L200" s="2"/>
+      <c r="O200" s="1"/>
+      <c r="P200" s="2"/>
+      <c r="Q200" s="2"/>
+      <c r="R200" s="2"/>
+      <c r="S200" s="2"/>
+    </row>
+    <row r="201" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A201" s="1">
         <v>2881700000</v>
       </c>
       <c r="B201" s="2">
-        <v>75.485799999999998</v>
+        <v>77.761399999999995</v>
       </c>
       <c r="C201" s="2">
-        <v>-43.448999999999998</v>
+        <v>43.091000000000001</v>
       </c>
       <c r="D201" s="2">
-        <v>54.801200000000001</v>
+        <v>56.786499999999997</v>
       </c>
       <c r="E201" s="2">
-        <v>-51.912599999999998</v>
-      </c>
-    </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+        <v>53.123699999999999</v>
+      </c>
+      <c r="H201" s="1"/>
+      <c r="I201" s="2"/>
+      <c r="J201" s="2"/>
+      <c r="K201" s="2"/>
+      <c r="L201" s="2"/>
+      <c r="O201" s="1"/>
+      <c r="P201" s="2"/>
+      <c r="Q201" s="2"/>
+      <c r="R201" s="2"/>
+      <c r="S201" s="2"/>
+    </row>
+    <row r="202" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A202" s="1">
         <v>3000000000</v>
       </c>
       <c r="B202" s="2">
-        <v>75.912999999999997</v>
+        <v>76.714600000000004</v>
       </c>
       <c r="C202" s="2">
-        <v>-43.625</v>
+        <v>44.421999999999997</v>
       </c>
       <c r="D202" s="2">
-        <v>54.951300000000003</v>
+        <v>54.789900000000003</v>
       </c>
       <c r="E202" s="2">
-        <v>-52.375</v>
-      </c>
+        <v>53.695500000000003</v>
+      </c>
+      <c r="H202" s="1"/>
+      <c r="I202" s="2"/>
+      <c r="J202" s="2"/>
+      <c r="K202" s="2"/>
+      <c r="L202" s="2"/>
+      <c r="O202" s="1"/>
+      <c r="P202" s="2"/>
+      <c r="Q202" s="2"/>
+      <c r="R202" s="2"/>
+      <c r="S202" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
